--- a/research/traditional_assets/database/data/macau/macau_chemical_basic.xlsx
+++ b/research/traditional_assets/database/data/macau/macau_chemical_basic.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09225059933771193</v>
+        <v>0.09203572722789084</v>
       </c>
       <c r="C2">
-        <v>77.28692979807971</v>
+        <v>76.54166248814229</v>
       </c>
       <c r="D2">
-        <v>35.88692979807971</v>
+        <v>35.9156624881423</v>
       </c>
       <c r="E2">
-        <v>-5.6</v>
+        <v>-4.826</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.7739999999999999</v>
       </c>
       <c r="G2">
         <v>41.4</v>
@@ -1445,28 +1445,28 @@
         <v>16</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.03893219999999999</v>
       </c>
       <c r="N2">
-        <v>16</v>
+        <v>15.9610678</v>
       </c>
       <c r="O2">
-        <v>4.2976</v>
+        <v>4.28714281108</v>
       </c>
       <c r="P2">
-        <v>11.7024</v>
+        <v>11.67392498892</v>
       </c>
       <c r="Q2">
-        <v>13.2024</v>
+        <v>13.17392498892</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09225059933771193</v>
+        <v>0.09259377073524327</v>
       </c>
       <c r="T2">
-        <v>0.9054086395470866</v>
+        <v>0.9120976888295587</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>410.9708673026441</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09203572722789084</v>
+        <v>0.09182085511806973</v>
       </c>
       <c r="C3">
-        <v>76.54166248814229</v>
+        <v>75.79644122443949</v>
       </c>
       <c r="D3">
-        <v>35.9156624881423</v>
+        <v>35.9444412244395</v>
       </c>
       <c r="E3">
-        <v>-4.826</v>
+        <v>-4.052</v>
       </c>
       <c r="F3">
-        <v>0.7739999999999999</v>
+        <v>1.548</v>
       </c>
       <c r="G3">
         <v>41.4</v>
@@ -1527,28 +1527,28 @@
         <v>16</v>
       </c>
       <c r="M3">
-        <v>0.03893219999999999</v>
+        <v>0.07786439999999999</v>
       </c>
       <c r="N3">
-        <v>15.9610678</v>
+        <v>15.9221356</v>
       </c>
       <c r="O3">
-        <v>4.28714281108</v>
+        <v>4.27668562216</v>
       </c>
       <c r="P3">
-        <v>11.67392498892</v>
+        <v>11.64544997784</v>
       </c>
       <c r="Q3">
-        <v>13.17392498892</v>
+        <v>13.14544997784</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09259377073524327</v>
+        <v>0.09294394563068339</v>
       </c>
       <c r="T3">
-        <v>0.9120976888295587</v>
+        <v>0.9189232493218771</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>410.9708673026441</v>
+        <v>205.4854336513221</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09182085511806973</v>
+        <v>0.09160598300824865</v>
       </c>
       <c r="C4">
-        <v>75.79644122443949</v>
+        <v>75.05126611774874</v>
       </c>
       <c r="D4">
-        <v>35.9444412244395</v>
+        <v>35.97326611774874</v>
       </c>
       <c r="E4">
-        <v>-4.052</v>
+        <v>-3.278</v>
       </c>
       <c r="F4">
-        <v>1.548</v>
+        <v>2.322</v>
       </c>
       <c r="G4">
         <v>41.4</v>
@@ -1609,28 +1609,28 @@
         <v>16</v>
       </c>
       <c r="M4">
-        <v>0.07786439999999999</v>
+        <v>0.1167966</v>
       </c>
       <c r="N4">
-        <v>15.9221356</v>
+        <v>15.8832034</v>
       </c>
       <c r="O4">
-        <v>4.27668562216</v>
+        <v>4.26622843324</v>
       </c>
       <c r="P4">
-        <v>11.64544997784</v>
+        <v>11.61697496676</v>
       </c>
       <c r="Q4">
-        <v>13.14544997784</v>
+        <v>13.11697496676</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09294394563068339</v>
+        <v>0.09330134062706047</v>
       </c>
       <c r="T4">
-        <v>0.9189232493218771</v>
+        <v>0.9258895430202229</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>205.4854336513221</v>
+        <v>136.9902891008814</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09160598300824865</v>
+        <v>0.09139111089842755</v>
       </c>
       <c r="C5">
-        <v>75.05126611774874</v>
+        <v>74.30613727920311</v>
       </c>
       <c r="D5">
-        <v>35.97326611774874</v>
+        <v>36.00213727920311</v>
       </c>
       <c r="E5">
-        <v>-3.278</v>
+        <v>-2.504</v>
       </c>
       <c r="F5">
-        <v>2.322</v>
+        <v>3.096</v>
       </c>
       <c r="G5">
         <v>41.4</v>
@@ -1691,28 +1691,28 @@
         <v>16</v>
       </c>
       <c r="M5">
-        <v>0.1167966</v>
+        <v>0.1557288</v>
       </c>
       <c r="N5">
-        <v>15.8832034</v>
+        <v>15.8442712</v>
       </c>
       <c r="O5">
-        <v>4.26622843324</v>
+        <v>4.25577124432</v>
       </c>
       <c r="P5">
-        <v>11.61697496676</v>
+        <v>11.58849995568</v>
       </c>
       <c r="Q5">
-        <v>13.11697496676</v>
+        <v>13.08849995568</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09330134062706047</v>
+        <v>0.0936661813525287</v>
       </c>
       <c r="T5">
-        <v>0.9258895430202229</v>
+        <v>0.9330009678372841</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>136.9902891008814</v>
+        <v>102.742716825661</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09139111089842755</v>
+        <v>0.09117623878860645</v>
       </c>
       <c r="C6">
-        <v>74.30613727920311</v>
+        <v>73.56105482029272</v>
       </c>
       <c r="D6">
-        <v>36.00213727920311</v>
+        <v>36.03105482029273</v>
       </c>
       <c r="E6">
-        <v>-2.504</v>
+        <v>-1.73</v>
       </c>
       <c r="F6">
-        <v>3.096</v>
+        <v>3.87</v>
       </c>
       <c r="G6">
         <v>41.4</v>
@@ -1773,28 +1773,28 @@
         <v>16</v>
       </c>
       <c r="M6">
-        <v>0.1557288</v>
+        <v>0.194661</v>
       </c>
       <c r="N6">
-        <v>15.8442712</v>
+        <v>15.805339</v>
       </c>
       <c r="O6">
-        <v>4.25577124432</v>
+        <v>4.2453140554</v>
       </c>
       <c r="P6">
-        <v>11.58849995568</v>
+        <v>11.5600249446</v>
       </c>
       <c r="Q6">
-        <v>13.08849995568</v>
+        <v>13.0600249446</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0936661813525287</v>
+        <v>0.09403870293537522</v>
       </c>
       <c r="T6">
-        <v>0.9330009678372841</v>
+        <v>0.9402621068610203</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>102.742716825661</v>
+        <v>82.19417346052883</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09117623878860645</v>
+        <v>0.09096136667878536</v>
       </c>
       <c r="C7">
-        <v>73.56105482029272</v>
+        <v>72.81601885286622</v>
       </c>
       <c r="D7">
-        <v>36.03105482029273</v>
+        <v>36.06001885286623</v>
       </c>
       <c r="E7">
-        <v>-1.73</v>
+        <v>-0.9559999999999995</v>
       </c>
       <c r="F7">
-        <v>3.87</v>
+        <v>4.644</v>
       </c>
       <c r="G7">
         <v>41.4</v>
@@ -1855,28 +1855,28 @@
         <v>16</v>
       </c>
       <c r="M7">
-        <v>0.194661</v>
+        <v>0.2335932</v>
       </c>
       <c r="N7">
-        <v>15.805339</v>
+        <v>15.7664068</v>
       </c>
       <c r="O7">
-        <v>4.2453140554</v>
+        <v>4.23485686648</v>
       </c>
       <c r="P7">
-        <v>11.5600249446</v>
+        <v>11.53154993352</v>
       </c>
       <c r="Q7">
-        <v>13.0600249446</v>
+        <v>13.03154993352</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09403870293537522</v>
+        <v>0.09441915050934613</v>
       </c>
       <c r="T7">
-        <v>0.9402621068610203</v>
+        <v>0.9476777382044104</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>82.19417346052883</v>
+        <v>68.49514455044068</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09096136667878536</v>
+        <v>0.09074649456896428</v>
       </c>
       <c r="C8">
-        <v>72.81601885286622</v>
+        <v>72.07102948913214</v>
       </c>
       <c r="D8">
-        <v>36.06001885286623</v>
+        <v>36.08902948913215</v>
       </c>
       <c r="E8">
-        <v>-0.9560000000000004</v>
+        <v>-0.1820000000000004</v>
       </c>
       <c r="F8">
-        <v>4.643999999999999</v>
+        <v>5.417999999999999</v>
       </c>
       <c r="G8">
         <v>41.4</v>
@@ -1937,28 +1937,28 @@
         <v>16</v>
       </c>
       <c r="M8">
-        <v>0.2335931999999999</v>
+        <v>0.2725254</v>
       </c>
       <c r="N8">
-        <v>15.7664068</v>
+        <v>15.7274746</v>
       </c>
       <c r="O8">
-        <v>4.23485686648</v>
+        <v>4.22439967756</v>
       </c>
       <c r="P8">
-        <v>11.53154993352</v>
+        <v>11.50307492244</v>
       </c>
       <c r="Q8">
-        <v>13.03154993352</v>
+        <v>13.00307492244</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09441915050934613</v>
+        <v>0.09480777975157448</v>
       </c>
       <c r="T8">
-        <v>0.9476777382044104</v>
+        <v>0.955252845490669</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>68.4951445504407</v>
+        <v>58.71012390037774</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09074649456896428</v>
+        <v>0.09053162245914319</v>
       </c>
       <c r="C9">
-        <v>72.07102948913214</v>
+        <v>71.32608684166046</v>
       </c>
       <c r="D9">
-        <v>36.08902948913215</v>
+        <v>36.11808684166044</v>
       </c>
       <c r="E9">
-        <v>-0.1819999999999995</v>
+        <v>0.5919999999999996</v>
       </c>
       <c r="F9">
-        <v>5.418</v>
+        <v>6.191999999999999</v>
       </c>
       <c r="G9">
         <v>41.4</v>
@@ -2019,28 +2019,28 @@
         <v>16</v>
       </c>
       <c r="M9">
-        <v>0.2725254</v>
+        <v>0.3114575999999999</v>
       </c>
       <c r="N9">
-        <v>15.7274746</v>
+        <v>15.6885424</v>
       </c>
       <c r="O9">
-        <v>4.22439967756</v>
+        <v>4.21394248864</v>
       </c>
       <c r="P9">
-        <v>11.50307492244</v>
+        <v>11.47459991136</v>
       </c>
       <c r="Q9">
-        <v>13.00307492244</v>
+        <v>12.97459991136</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09480777975157449</v>
+        <v>0.09520485745559042</v>
       </c>
       <c r="T9">
-        <v>0.9552528454906692</v>
+        <v>0.9629926290222814</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>58.71012390037774</v>
+        <v>51.37135841283052</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09053162245914319</v>
+        <v>0.09031675034932207</v>
       </c>
       <c r="C10">
-        <v>71.32608684166046</v>
+        <v>70.58119102338388</v>
       </c>
       <c r="D10">
-        <v>36.11808684166044</v>
+        <v>36.14719102338388</v>
       </c>
       <c r="E10">
-        <v>0.5919999999999996</v>
+        <v>1.366</v>
       </c>
       <c r="F10">
-        <v>6.191999999999999</v>
+        <v>6.965999999999999</v>
       </c>
       <c r="G10">
         <v>41.4</v>
@@ -2101,28 +2101,28 @@
         <v>16</v>
       </c>
       <c r="M10">
-        <v>0.3114575999999999</v>
+        <v>0.3503898</v>
       </c>
       <c r="N10">
-        <v>15.6885424</v>
+        <v>15.6496102</v>
       </c>
       <c r="O10">
-        <v>4.21394248864</v>
+        <v>4.20348529972</v>
       </c>
       <c r="P10">
-        <v>11.47459991136</v>
+        <v>11.44612490028</v>
       </c>
       <c r="Q10">
-        <v>12.97459991136</v>
+        <v>12.94612490028</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09520485745559042</v>
+        <v>0.09561066214211217</v>
       </c>
       <c r="T10">
-        <v>0.9629926290222814</v>
+        <v>0.9709025176864564</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>51.37135841283052</v>
+        <v>45.66342970029379</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09031675034932207</v>
+        <v>0.09010187823950098</v>
       </c>
       <c r="C11">
-        <v>70.58119102338388</v>
+        <v>69.83634214759952</v>
       </c>
       <c r="D11">
-        <v>36.14719102338388</v>
+        <v>36.17634214759952</v>
       </c>
       <c r="E11">
-        <v>1.366</v>
+        <v>2.139999999999999</v>
       </c>
       <c r="F11">
-        <v>6.965999999999999</v>
+        <v>7.739999999999998</v>
       </c>
       <c r="G11">
         <v>41.4</v>
@@ -2183,28 +2183,28 @@
         <v>16</v>
       </c>
       <c r="M11">
-        <v>0.3503898</v>
+        <v>0.3893219999999999</v>
       </c>
       <c r="N11">
-        <v>15.6496102</v>
+        <v>15.610678</v>
       </c>
       <c r="O11">
-        <v>4.20348529972</v>
+        <v>4.1930281108</v>
       </c>
       <c r="P11">
-        <v>11.44612490028</v>
+        <v>11.4176498892</v>
       </c>
       <c r="Q11">
-        <v>12.94612490028</v>
+        <v>12.9176498892</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09561066214211217</v>
+        <v>0.09602548471055665</v>
       </c>
       <c r="T11">
-        <v>0.9709025176864564</v>
+        <v>0.9789881816542798</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>45.66342970029379</v>
+        <v>41.09708673026442</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09010187823950098</v>
+        <v>0.0898870061296799</v>
       </c>
       <c r="C12">
-        <v>69.83634214759952</v>
+        <v>69.09154032797024</v>
       </c>
       <c r="D12">
-        <v>36.17634214759952</v>
+        <v>36.20554032797023</v>
       </c>
       <c r="E12">
-        <v>2.14</v>
+        <v>2.914</v>
       </c>
       <c r="F12">
-        <v>7.739999999999999</v>
+        <v>8.513999999999999</v>
       </c>
       <c r="G12">
         <v>41.4</v>
@@ -2265,28 +2265,28 @@
         <v>16</v>
       </c>
       <c r="M12">
-        <v>0.3893219999999999</v>
+        <v>0.4282541999999999</v>
       </c>
       <c r="N12">
-        <v>15.610678</v>
+        <v>15.5717458</v>
       </c>
       <c r="O12">
-        <v>4.1930281108</v>
+        <v>4.18257092188</v>
       </c>
       <c r="P12">
-        <v>11.4176498892</v>
+        <v>11.38917487812</v>
       </c>
       <c r="Q12">
-        <v>12.9176498892</v>
+        <v>12.88917487812</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09602548471055665</v>
+        <v>0.09644962913447179</v>
       </c>
       <c r="T12">
-        <v>0.9789881816542798</v>
+        <v>0.987255545935987</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>41.09708673026442</v>
+        <v>37.36098793660402</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0898870061296799</v>
+        <v>0.08967213401985881</v>
       </c>
       <c r="C13">
-        <v>69.09154032797024</v>
+        <v>68.34678567852609</v>
       </c>
       <c r="D13">
-        <v>36.20554032797023</v>
+        <v>36.23478567852609</v>
       </c>
       <c r="E13">
-        <v>2.914</v>
+        <v>3.687999999999999</v>
       </c>
       <c r="F13">
-        <v>8.513999999999999</v>
+        <v>9.287999999999998</v>
       </c>
       <c r="G13">
         <v>41.4</v>
@@ -2347,28 +2347,28 @@
         <v>16</v>
       </c>
       <c r="M13">
-        <v>0.4282541999999999</v>
+        <v>0.4671863999999999</v>
       </c>
       <c r="N13">
-        <v>15.5717458</v>
+        <v>15.5328136</v>
       </c>
       <c r="O13">
-        <v>4.18257092188</v>
+        <v>4.172113732960001</v>
       </c>
       <c r="P13">
-        <v>11.38917487812</v>
+        <v>11.36069986704</v>
       </c>
       <c r="Q13">
-        <v>12.88917487812</v>
+        <v>12.86069986704</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09644962913447179</v>
+        <v>0.09688341320438501</v>
       </c>
       <c r="T13">
-        <v>0.987255545935987</v>
+        <v>0.9957108048604603</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>37.36098793660402</v>
+        <v>34.24757227522035</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08967213401985881</v>
+        <v>0.08945726191003769</v>
       </c>
       <c r="C14">
-        <v>68.34678567852609</v>
+        <v>67.60207831366596</v>
       </c>
       <c r="D14">
-        <v>36.23478567852609</v>
+        <v>36.26407831366595</v>
       </c>
       <c r="E14">
-        <v>3.687999999999999</v>
+        <v>4.462</v>
       </c>
       <c r="F14">
-        <v>9.287999999999998</v>
+        <v>10.062</v>
       </c>
       <c r="G14">
         <v>41.4</v>
@@ -2429,28 +2429,28 @@
         <v>16</v>
       </c>
       <c r="M14">
-        <v>0.4671863999999999</v>
+        <v>0.5061186</v>
       </c>
       <c r="N14">
-        <v>15.5328136</v>
+        <v>15.4938814</v>
       </c>
       <c r="O14">
-        <v>4.172113732960001</v>
+        <v>4.16165654404</v>
       </c>
       <c r="P14">
-        <v>11.36069986704</v>
+        <v>11.33222485596</v>
       </c>
       <c r="Q14">
-        <v>12.86069986704</v>
+        <v>12.83222485596</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09688341320438501</v>
+        <v>0.09732716932188241</v>
       </c>
       <c r="T14">
-        <v>0.9957108048604603</v>
+        <v>1.004360437553312</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>34.24757227522035</v>
+        <v>31.61314363866493</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08945726191003769</v>
+        <v>0.08924238980021661</v>
       </c>
       <c r="C15">
-        <v>67.60207831366596</v>
+        <v>66.85741834815884</v>
       </c>
       <c r="D15">
-        <v>36.26407831366595</v>
+        <v>36.29341834815884</v>
       </c>
       <c r="E15">
-        <v>4.462</v>
+        <v>5.236000000000001</v>
       </c>
       <c r="F15">
-        <v>10.062</v>
+        <v>10.836</v>
       </c>
       <c r="G15">
         <v>41.4</v>
@@ -2511,28 +2511,28 @@
         <v>16</v>
       </c>
       <c r="M15">
-        <v>0.5061186</v>
+        <v>0.5450507999999999</v>
       </c>
       <c r="N15">
-        <v>15.4938814</v>
+        <v>15.4549492</v>
       </c>
       <c r="O15">
-        <v>4.16165654404</v>
+        <v>4.15119935512</v>
       </c>
       <c r="P15">
-        <v>11.33222485596</v>
+        <v>11.30374984488</v>
       </c>
       <c r="Q15">
-        <v>12.83222485596</v>
+        <v>12.80374984488</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09732716932188241</v>
+        <v>0.09778124534908908</v>
       </c>
       <c r="T15">
-        <v>1.004360437553312</v>
+        <v>1.013211224494835</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>31.61314363866493</v>
+        <v>29.35506195018887</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08924238980021661</v>
+        <v>0.08902751769039552</v>
       </c>
       <c r="C16">
-        <v>66.85741834815884</v>
+        <v>66.11280589714556</v>
       </c>
       <c r="D16">
-        <v>36.29341834815884</v>
+        <v>36.32280589714556</v>
       </c>
       <c r="E16">
-        <v>5.236000000000001</v>
+        <v>6.010000000000002</v>
       </c>
       <c r="F16">
-        <v>10.836</v>
+        <v>11.61</v>
       </c>
       <c r="G16">
         <v>41.4</v>
@@ -2593,28 +2593,28 @@
         <v>16</v>
       </c>
       <c r="M16">
-        <v>0.5450507999999999</v>
+        <v>0.583983</v>
       </c>
       <c r="N16">
-        <v>15.4549492</v>
+        <v>15.416017</v>
       </c>
       <c r="O16">
-        <v>4.15119935512</v>
+        <v>4.1407421662</v>
       </c>
       <c r="P16">
-        <v>11.30374984488</v>
+        <v>11.2752748338</v>
       </c>
       <c r="Q16">
-        <v>12.80374984488</v>
+        <v>12.7752748338</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09778124534908908</v>
+        <v>0.09824600551811238</v>
       </c>
       <c r="T16">
-        <v>1.013211224494835</v>
+        <v>1.022270265246747</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>29.35506195018887</v>
+        <v>27.39805782017627</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08902751769039551</v>
+        <v>0.08881264558057442</v>
       </c>
       <c r="C17">
-        <v>66.11280589714556</v>
+        <v>65.36824107614011</v>
       </c>
       <c r="D17">
-        <v>36.32280589714556</v>
+        <v>36.35224107614011</v>
       </c>
       <c r="E17">
-        <v>6.009999999999998</v>
+        <v>6.783999999999999</v>
       </c>
       <c r="F17">
-        <v>11.61</v>
+        <v>12.384</v>
       </c>
       <c r="G17">
         <v>41.4</v>
@@ -2675,28 +2675,28 @@
         <v>16</v>
       </c>
       <c r="M17">
-        <v>0.5839829999999998</v>
+        <v>0.6229151999999999</v>
       </c>
       <c r="N17">
-        <v>15.416017</v>
+        <v>15.3770848</v>
       </c>
       <c r="O17">
-        <v>4.1407421662</v>
+        <v>4.130284977280001</v>
       </c>
       <c r="P17">
-        <v>11.2752748338</v>
+        <v>11.24679982272</v>
       </c>
       <c r="Q17">
-        <v>12.7752748338</v>
+        <v>12.74679982272</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09824600551811237</v>
+        <v>0.09872183140544574</v>
       </c>
       <c r="T17">
-        <v>1.022270265246746</v>
+        <v>1.031544997445132</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>27.39805782017628</v>
+        <v>25.68567920641526</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08881264558057442</v>
+        <v>0.08859777347075333</v>
       </c>
       <c r="C18">
-        <v>65.36824107614011</v>
+        <v>64.62372400103125</v>
       </c>
       <c r="D18">
-        <v>36.35224107614011</v>
+        <v>36.38172400103124</v>
       </c>
       <c r="E18">
-        <v>6.783999999999999</v>
+        <v>7.558</v>
       </c>
       <c r="F18">
-        <v>12.384</v>
+        <v>13.158</v>
       </c>
       <c r="G18">
         <v>41.4</v>
@@ -2757,28 +2757,28 @@
         <v>16</v>
       </c>
       <c r="M18">
-        <v>0.6229151999999999</v>
+        <v>0.6618474</v>
       </c>
       <c r="N18">
-        <v>15.3770848</v>
+        <v>15.3381526</v>
       </c>
       <c r="O18">
-        <v>4.130284977280001</v>
+        <v>4.11982778836</v>
       </c>
       <c r="P18">
-        <v>11.24679982272</v>
+        <v>11.21832481164</v>
       </c>
       <c r="Q18">
-        <v>12.74679982272</v>
+        <v>12.71832481164</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09872183140544574</v>
+        <v>0.09920912297681124</v>
       </c>
       <c r="T18">
-        <v>1.031544997445132</v>
+        <v>1.041043217166371</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>25.68567920641526</v>
+        <v>24.17475690015554</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08859777347075333</v>
+        <v>0.08838290136093224</v>
       </c>
       <c r="C19">
-        <v>64.62372400103125</v>
+        <v>63.87925478808397</v>
       </c>
       <c r="D19">
-        <v>36.38172400103124</v>
+        <v>36.41125478808397</v>
       </c>
       <c r="E19">
-        <v>7.558</v>
+        <v>8.332000000000001</v>
       </c>
       <c r="F19">
-        <v>13.158</v>
+        <v>13.932</v>
       </c>
       <c r="G19">
         <v>41.4</v>
@@ -2839,28 +2839,28 @@
         <v>16</v>
       </c>
       <c r="M19">
-        <v>0.6618474</v>
+        <v>0.7007795999999999</v>
       </c>
       <c r="N19">
-        <v>15.3381526</v>
+        <v>15.2992204</v>
       </c>
       <c r="O19">
-        <v>4.11982778836</v>
+        <v>4.10937059944</v>
       </c>
       <c r="P19">
-        <v>11.21832481164</v>
+        <v>11.18984980056</v>
       </c>
       <c r="Q19">
-        <v>12.71832481164</v>
+        <v>12.68984980056</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09920912297681124</v>
+        <v>0.09970829970845396</v>
       </c>
       <c r="T19">
-        <v>1.041043217166371</v>
+        <v>1.050773100783249</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>24.17475690015554</v>
+        <v>22.83171485014689</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08838290136093226</v>
+        <v>0.08816802925111114</v>
       </c>
       <c r="C20">
-        <v>63.87925478808397</v>
+        <v>63.1348335539411</v>
       </c>
       <c r="D20">
-        <v>36.41125478808397</v>
+        <v>36.4408335539411</v>
       </c>
       <c r="E20">
-        <v>8.331999999999999</v>
+        <v>9.105999999999998</v>
       </c>
       <c r="F20">
-        <v>13.932</v>
+        <v>14.706</v>
       </c>
       <c r="G20">
         <v>41.4</v>
@@ -2921,28 +2921,28 @@
         <v>16</v>
       </c>
       <c r="M20">
-        <v>0.7007795999999999</v>
+        <v>0.7397117999999998</v>
       </c>
       <c r="N20">
-        <v>15.2992204</v>
+        <v>15.2602882</v>
       </c>
       <c r="O20">
-        <v>4.10937059944</v>
+        <v>4.09891341052</v>
       </c>
       <c r="P20">
-        <v>11.18984980056</v>
+        <v>11.16137478948</v>
       </c>
       <c r="Q20">
-        <v>12.68984980056</v>
+        <v>12.66137478948</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09970829970845396</v>
+        <v>0.1002198017914952</v>
       </c>
       <c r="T20">
-        <v>1.050773100783249</v>
+        <v>1.06074322844005</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>22.83171485014689</v>
+        <v>21.63004564750759</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08816802925111114</v>
+        <v>0.08795315714129005</v>
       </c>
       <c r="C21">
-        <v>63.1348335539411</v>
+        <v>62.39046041562477</v>
       </c>
       <c r="D21">
-        <v>36.4408335539411</v>
+        <v>36.47046041562477</v>
       </c>
       <c r="E21">
-        <v>9.105999999999998</v>
+        <v>9.879999999999999</v>
       </c>
       <c r="F21">
-        <v>14.706</v>
+        <v>15.48</v>
       </c>
       <c r="G21">
         <v>41.4</v>
@@ -3003,28 +3003,28 @@
         <v>16</v>
       </c>
       <c r="M21">
-        <v>0.7397117999999998</v>
+        <v>0.7786439999999999</v>
       </c>
       <c r="N21">
-        <v>15.2602882</v>
+        <v>15.221356</v>
       </c>
       <c r="O21">
-        <v>4.09891341052</v>
+        <v>4.0884562216</v>
       </c>
       <c r="P21">
-        <v>11.16137478948</v>
+        <v>11.1328997784</v>
       </c>
       <c r="Q21">
-        <v>12.66137478948</v>
+        <v>12.6328997784</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1002198017914952</v>
+        <v>0.1007440914266126</v>
       </c>
       <c r="T21">
-        <v>1.06074322844005</v>
+        <v>1.070962609288271</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>21.63004564750759</v>
+        <v>20.54854336513221</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08795315714129005</v>
+        <v>0.08773828503146895</v>
       </c>
       <c r="C22">
-        <v>62.39046041562477</v>
+        <v>61.64613549053799</v>
       </c>
       <c r="D22">
-        <v>36.47046041562477</v>
+        <v>36.50013549053799</v>
       </c>
       <c r="E22">
-        <v>9.879999999999999</v>
+        <v>10.654</v>
       </c>
       <c r="F22">
-        <v>15.48</v>
+        <v>16.254</v>
       </c>
       <c r="G22">
         <v>41.4</v>
@@ -3085,28 +3085,28 @@
         <v>16</v>
       </c>
       <c r="M22">
-        <v>0.7786439999999999</v>
+        <v>0.8175762</v>
       </c>
       <c r="N22">
-        <v>15.221356</v>
+        <v>15.1824238</v>
       </c>
       <c r="O22">
-        <v>4.0884562216</v>
+        <v>4.07799903268</v>
       </c>
       <c r="P22">
-        <v>11.1328997784</v>
+        <v>11.10442476732</v>
       </c>
       <c r="Q22">
-        <v>12.6328997784</v>
+        <v>12.60442476732</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1007440914266126</v>
+        <v>0.1012816542170493</v>
       </c>
       <c r="T22">
-        <v>1.070962609288271</v>
+        <v>1.081440708638979</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>20.54854336513221</v>
+        <v>19.57004130012591</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08773828503146895</v>
+        <v>0.08752341292164788</v>
       </c>
       <c r="C23">
-        <v>61.64613549053799</v>
+        <v>60.9018588964662</v>
       </c>
       <c r="D23">
-        <v>36.50013549053799</v>
+        <v>36.5298588964662</v>
       </c>
       <c r="E23">
-        <v>10.654</v>
+        <v>11.428</v>
       </c>
       <c r="F23">
-        <v>16.254</v>
+        <v>17.028</v>
       </c>
       <c r="G23">
         <v>41.4</v>
@@ -3167,28 +3167,28 @@
         <v>16</v>
       </c>
       <c r="M23">
-        <v>0.8175761999999999</v>
+        <v>0.8565083999999998</v>
       </c>
       <c r="N23">
-        <v>15.1824238</v>
+        <v>15.1434916</v>
       </c>
       <c r="O23">
-        <v>4.07799903268</v>
+        <v>4.06754184376</v>
       </c>
       <c r="P23">
-        <v>11.10442476732</v>
+        <v>11.07594975624</v>
       </c>
       <c r="Q23">
-        <v>12.60442476732</v>
+        <v>12.57594975624</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1012816542170493</v>
+        <v>0.1018330006687793</v>
       </c>
       <c r="T23">
-        <v>1.081440708638979</v>
+        <v>1.092187477203808</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>19.57004130012591</v>
+        <v>18.68049396830201</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08752341292164788</v>
+        <v>0.08730854081182678</v>
       </c>
       <c r="C24">
-        <v>60.9018588964662</v>
+        <v>60.1576307515788</v>
       </c>
       <c r="D24">
-        <v>36.5298588964662</v>
+        <v>36.5596307515788</v>
       </c>
       <c r="E24">
-        <v>11.428</v>
+        <v>12.202</v>
       </c>
       <c r="F24">
-        <v>17.028</v>
+        <v>17.802</v>
       </c>
       <c r="G24">
         <v>41.4</v>
@@ -3249,28 +3249,28 @@
         <v>16</v>
       </c>
       <c r="M24">
-        <v>0.8565083999999998</v>
+        <v>0.8954405999999999</v>
       </c>
       <c r="N24">
-        <v>15.1434916</v>
+        <v>15.1045594</v>
       </c>
       <c r="O24">
-        <v>4.06754184376</v>
+        <v>4.05708465484</v>
       </c>
       <c r="P24">
-        <v>11.07594975624</v>
+        <v>11.04747474516</v>
       </c>
       <c r="Q24">
-        <v>12.57594975624</v>
+        <v>12.54747474516</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1018330006687793</v>
+        <v>0.1023986678075672</v>
       </c>
       <c r="T24">
-        <v>1.092187477203808</v>
+        <v>1.103213382614476</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>18.68049396830201</v>
+        <v>17.86829857837583</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08730854081182678</v>
+        <v>0.08709366870200566</v>
       </c>
       <c r="C25">
-        <v>60.1576307515788</v>
+        <v>59.41345117443074</v>
       </c>
       <c r="D25">
-        <v>36.5596307515788</v>
+        <v>36.58945117443075</v>
       </c>
       <c r="E25">
-        <v>12.202</v>
+        <v>12.976</v>
       </c>
       <c r="F25">
-        <v>17.802</v>
+        <v>18.576</v>
       </c>
       <c r="G25">
         <v>41.4</v>
@@ -3331,28 +3331,28 @@
         <v>16</v>
       </c>
       <c r="M25">
-        <v>0.8954405999999999</v>
+        <v>0.9343728</v>
       </c>
       <c r="N25">
-        <v>15.1045594</v>
+        <v>15.0656272</v>
       </c>
       <c r="O25">
-        <v>4.05708465484</v>
+        <v>4.04662746592</v>
       </c>
       <c r="P25">
-        <v>11.04747474516</v>
+        <v>11.01899973408</v>
       </c>
       <c r="Q25">
-        <v>12.54747474516</v>
+        <v>12.51899973408</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1023986678075672</v>
+        <v>0.1029792209236917</v>
       </c>
       <c r="T25">
-        <v>1.103213382614476</v>
+        <v>1.114529443430688</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>17.86829857837583</v>
+        <v>17.12378613761017</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08709366870200566</v>
+        <v>0.08687879659218457</v>
       </c>
       <c r="C26">
-        <v>59.41345117443075</v>
+        <v>58.66932028396413</v>
       </c>
       <c r="D26">
-        <v>36.58945117443075</v>
+        <v>36.61932028396412</v>
       </c>
       <c r="E26">
-        <v>12.976</v>
+        <v>13.75</v>
       </c>
       <c r="F26">
-        <v>18.576</v>
+        <v>19.35</v>
       </c>
       <c r="G26">
         <v>41.4</v>
@@ -3413,28 +3413,28 @@
         <v>16</v>
       </c>
       <c r="M26">
-        <v>0.9343727999999998</v>
+        <v>0.9733049999999999</v>
       </c>
       <c r="N26">
-        <v>15.0656272</v>
+        <v>15.026695</v>
       </c>
       <c r="O26">
-        <v>4.04662746592</v>
+        <v>4.036170277</v>
       </c>
       <c r="P26">
-        <v>11.01899973408</v>
+        <v>10.990524723</v>
       </c>
       <c r="Q26">
-        <v>12.51899973408</v>
+        <v>12.490524723</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1029792209236917</v>
+        <v>0.1035752554562461</v>
       </c>
       <c r="T26">
-        <v>1.114529443430688</v>
+        <v>1.126147265868666</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>17.12378613761017</v>
+        <v>16.43883469210576</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08687879659218457</v>
+        <v>0.08666392448236349</v>
       </c>
       <c r="C27">
-        <v>58.66932028396413</v>
+        <v>57.92523819950972</v>
       </c>
       <c r="D27">
-        <v>36.61932028396412</v>
+        <v>36.64923819950971</v>
       </c>
       <c r="E27">
-        <v>13.75</v>
+        <v>14.524</v>
       </c>
       <c r="F27">
-        <v>19.35</v>
+        <v>20.124</v>
       </c>
       <c r="G27">
         <v>41.4</v>
@@ -3495,28 +3495,28 @@
         <v>16</v>
       </c>
       <c r="M27">
-        <v>0.9733049999999999</v>
+        <v>1.0122372</v>
       </c>
       <c r="N27">
-        <v>15.026695</v>
+        <v>14.9877628</v>
       </c>
       <c r="O27">
-        <v>4.036170277</v>
+        <v>4.02571308808</v>
       </c>
       <c r="P27">
-        <v>10.990524723</v>
+        <v>10.96204971192</v>
       </c>
       <c r="Q27">
-        <v>12.490524723</v>
+        <v>12.46204971192</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1035752554562461</v>
+        <v>0.1041873990302209</v>
       </c>
       <c r="T27">
-        <v>1.126147265868666</v>
+        <v>1.138079083507671</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>16.43883469210576</v>
+        <v>15.80657181933247</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08666392448236349</v>
+        <v>0.08644905237254238</v>
       </c>
       <c r="C28">
-        <v>57.92523819950972</v>
+        <v>57.18120504078857</v>
       </c>
       <c r="D28">
-        <v>36.64923819950971</v>
+        <v>36.67920504078857</v>
       </c>
       <c r="E28">
-        <v>14.524</v>
+        <v>15.298</v>
       </c>
       <c r="F28">
-        <v>20.124</v>
+        <v>20.898</v>
       </c>
       <c r="G28">
         <v>41.4</v>
@@ -3577,28 +3577,28 @@
         <v>16</v>
       </c>
       <c r="M28">
-        <v>1.0122372</v>
+        <v>1.0511694</v>
       </c>
       <c r="N28">
-        <v>14.9877628</v>
+        <v>14.9488306</v>
       </c>
       <c r="O28">
-        <v>4.02571308808</v>
+        <v>4.01525589916</v>
       </c>
       <c r="P28">
-        <v>10.96204971192</v>
+        <v>10.93357470084</v>
       </c>
       <c r="Q28">
-        <v>12.46204971192</v>
+        <v>12.43357470084</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1041873990302209</v>
+        <v>0.104816313661017</v>
       </c>
       <c r="T28">
-        <v>1.138079083507671</v>
+        <v>1.150337800260072</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>15.80657181933247</v>
+        <v>15.22114323343126</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08644905237254238</v>
+        <v>0.0862341802627213</v>
       </c>
       <c r="C29">
-        <v>57.18120504078857</v>
+        <v>56.43722092791369</v>
       </c>
       <c r="D29">
-        <v>36.67920504078857</v>
+        <v>36.70922092791368</v>
       </c>
       <c r="E29">
-        <v>15.298</v>
+        <v>16.072</v>
       </c>
       <c r="F29">
-        <v>20.898</v>
+        <v>21.672</v>
       </c>
       <c r="G29">
         <v>41.4</v>
@@ -3659,28 +3659,28 @@
         <v>16</v>
       </c>
       <c r="M29">
-        <v>1.0511694</v>
+        <v>1.0901016</v>
       </c>
       <c r="N29">
-        <v>14.9488306</v>
+        <v>14.9098984</v>
       </c>
       <c r="O29">
-        <v>4.01525589916</v>
+        <v>4.00479871024</v>
       </c>
       <c r="P29">
-        <v>10.93357470084</v>
+        <v>10.90509968976</v>
       </c>
       <c r="Q29">
-        <v>12.43357470084</v>
+        <v>12.40509968976</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.104816313661017</v>
+        <v>0.1054626981426685</v>
       </c>
       <c r="T29">
-        <v>1.150337800260072</v>
+        <v>1.162937036922263</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>15.22114323343126</v>
+        <v>14.67753097509443</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0862341802627213</v>
+        <v>0.0860193081529002</v>
       </c>
       <c r="C30">
-        <v>56.43722092791369</v>
+        <v>55.69328598139148</v>
       </c>
       <c r="D30">
-        <v>36.70922092791368</v>
+        <v>36.73928598139148</v>
       </c>
       <c r="E30">
-        <v>16.072</v>
+        <v>16.846</v>
       </c>
       <c r="F30">
-        <v>21.672</v>
+        <v>22.446</v>
       </c>
       <c r="G30">
         <v>41.4</v>
@@ -3741,28 +3741,28 @@
         <v>16</v>
       </c>
       <c r="M30">
-        <v>1.0901016</v>
+        <v>1.1290338</v>
       </c>
       <c r="N30">
-        <v>14.9098984</v>
+        <v>14.8709662</v>
       </c>
       <c r="O30">
-        <v>4.00479871024</v>
+        <v>3.99434152132</v>
       </c>
       <c r="P30">
-        <v>10.90509968976</v>
+        <v>10.87662467868</v>
       </c>
       <c r="Q30">
-        <v>12.40509968976</v>
+        <v>12.37662467868</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1054626981426685</v>
+        <v>0.1061272906378876</v>
       </c>
       <c r="T30">
-        <v>1.162937036922263</v>
+        <v>1.175891181659445</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>14.67753097509443</v>
+        <v>14.17140921733255</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0860193081529002</v>
+        <v>0.08580443604307909</v>
       </c>
       <c r="C31">
-        <v>55.69328598139148</v>
+        <v>54.94940032212352</v>
       </c>
       <c r="D31">
-        <v>36.73928598139148</v>
+        <v>36.76940032212353</v>
       </c>
       <c r="E31">
-        <v>16.846</v>
+        <v>17.62</v>
       </c>
       <c r="F31">
-        <v>22.44599999999999</v>
+        <v>23.22</v>
       </c>
       <c r="G31">
         <v>41.4</v>
@@ -3823,28 +3823,28 @@
         <v>16</v>
       </c>
       <c r="M31">
-        <v>1.1290338</v>
+        <v>1.167966</v>
       </c>
       <c r="N31">
-        <v>14.8709662</v>
+        <v>14.832034</v>
       </c>
       <c r="O31">
-        <v>3.99434152132</v>
+        <v>3.9838843324</v>
       </c>
       <c r="P31">
-        <v>10.87662467868</v>
+        <v>10.8481496676</v>
       </c>
       <c r="Q31">
-        <v>12.37662467868</v>
+        <v>12.3481496676</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1061272906378876</v>
+        <v>0.106810871490113</v>
       </c>
       <c r="T31">
-        <v>1.175891181659445</v>
+        <v>1.189215444817689</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>14.17140921733256</v>
+        <v>13.69902891008814</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08580443604307909</v>
+        <v>0.08558956393325801</v>
       </c>
       <c r="C32">
-        <v>54.94940032212352</v>
+        <v>54.20556407140811</v>
       </c>
       <c r="D32">
-        <v>36.76940032212353</v>
+        <v>36.79956407140811</v>
       </c>
       <c r="E32">
-        <v>17.62</v>
+        <v>18.394</v>
       </c>
       <c r="F32">
-        <v>23.22</v>
+        <v>23.994</v>
       </c>
       <c r="G32">
         <v>41.4</v>
@@ -3905,28 +3905,28 @@
         <v>16</v>
       </c>
       <c r="M32">
-        <v>1.167966</v>
+        <v>1.2068982</v>
       </c>
       <c r="N32">
-        <v>14.832034</v>
+        <v>14.7931018</v>
       </c>
       <c r="O32">
-        <v>3.9838843324</v>
+        <v>3.97342714348</v>
       </c>
       <c r="P32">
-        <v>10.8481496676</v>
+        <v>10.81967465652</v>
       </c>
       <c r="Q32">
-        <v>12.3481496676</v>
+        <v>12.31967465652</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.106810871490113</v>
+        <v>0.1075142662800841</v>
       </c>
       <c r="T32">
-        <v>1.189215444817689</v>
+        <v>1.202925918502259</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>13.69902891008814</v>
+        <v>13.2571247516982</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08558956393325801</v>
+        <v>0.08572576382343691</v>
       </c>
       <c r="C33">
-        <v>54.20556407140811</v>
+        <v>53.41243858944</v>
       </c>
       <c r="D33">
-        <v>36.79956407140811</v>
+        <v>36.78043858944</v>
       </c>
       <c r="E33">
-        <v>18.394</v>
+        <v>19.168</v>
       </c>
       <c r="F33">
-        <v>23.994</v>
+        <v>24.768</v>
       </c>
       <c r="G33">
         <v>41.4</v>
@@ -3987,45 +3987,45 @@
         <v>16</v>
       </c>
       <c r="M33">
-        <v>1.2068982</v>
+        <v>1.2829824</v>
       </c>
       <c r="N33">
-        <v>14.7931018</v>
+        <v>14.7170176</v>
       </c>
       <c r="O33">
-        <v>3.97342714348</v>
+        <v>3.95299092736</v>
       </c>
       <c r="P33">
-        <v>10.81967465652</v>
+        <v>10.76402667264</v>
       </c>
       <c r="Q33">
-        <v>12.31967465652</v>
+        <v>12.26402667264</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1075142662800841</v>
+        <v>0.1082383491521131</v>
       </c>
       <c r="T33">
-        <v>1.202925918502259</v>
+        <v>1.217039641412846</v>
       </c>
       <c r="U33">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V33">
         <v>0.2686</v>
       </c>
       <c r="W33">
-        <v>0.03678942</v>
+        <v>0.03788652</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y33">
-        <v>13.2571247516982</v>
+        <v>12.47094270350084</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08572576382343691</v>
+        <v>0.08552186271361581</v>
       </c>
       <c r="C34">
-        <v>53.41243858944</v>
+        <v>52.66707822507914</v>
       </c>
       <c r="D34">
-        <v>36.78043858944</v>
+        <v>36.80907822507913</v>
       </c>
       <c r="E34">
-        <v>19.168</v>
+        <v>19.942</v>
       </c>
       <c r="F34">
-        <v>24.768</v>
+        <v>25.542</v>
       </c>
       <c r="G34">
         <v>41.4</v>
@@ -4069,28 +4069,28 @@
         <v>16</v>
       </c>
       <c r="M34">
-        <v>1.2829824</v>
+        <v>1.3230756</v>
       </c>
       <c r="N34">
-        <v>14.7170176</v>
+        <v>14.6769244</v>
       </c>
       <c r="O34">
-        <v>3.95299092736</v>
+        <v>3.94222189384</v>
       </c>
       <c r="P34">
-        <v>10.76402667264</v>
+        <v>10.73470250616</v>
       </c>
       <c r="Q34">
-        <v>12.26402667264</v>
+        <v>12.23470250616</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1082383491521131</v>
+        <v>0.1089840464382326</v>
       </c>
       <c r="T34">
-        <v>1.217039641412846</v>
+        <v>1.231574669484943</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>12.47094270350084</v>
+        <v>12.0930353488493</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08552186271361581</v>
+        <v>0.08531796160379472</v>
       </c>
       <c r="C35">
-        <v>52.66707822507914</v>
+        <v>51.92176249683149</v>
       </c>
       <c r="D35">
-        <v>36.80907822507913</v>
+        <v>36.83776249683149</v>
       </c>
       <c r="E35">
-        <v>19.942</v>
+        <v>20.716</v>
       </c>
       <c r="F35">
-        <v>25.542</v>
+        <v>26.316</v>
       </c>
       <c r="G35">
         <v>41.4</v>
@@ -4151,28 +4151,28 @@
         <v>16</v>
       </c>
       <c r="M35">
-        <v>1.3230756</v>
+        <v>1.3631688</v>
       </c>
       <c r="N35">
-        <v>14.6769244</v>
+        <v>14.6368312</v>
       </c>
       <c r="O35">
-        <v>3.94222189384</v>
+        <v>3.93145286032</v>
       </c>
       <c r="P35">
-        <v>10.73470250616</v>
+        <v>10.70537833968</v>
       </c>
       <c r="Q35">
-        <v>12.23470250616</v>
+        <v>12.20537833968</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1089840464382326</v>
+        <v>0.1097523406118102</v>
       </c>
       <c r="T35">
-        <v>1.231574669484943</v>
+        <v>1.246550152953164</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>12.0930353488493</v>
+        <v>11.73735783858903</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08531796160379472</v>
+        <v>0.08511406049397362</v>
       </c>
       <c r="C36">
-        <v>51.92176249683149</v>
+        <v>51.17649150912942</v>
       </c>
       <c r="D36">
-        <v>36.83776249683149</v>
+        <v>36.86649150912942</v>
       </c>
       <c r="E36">
-        <v>20.716</v>
+        <v>21.49</v>
       </c>
       <c r="F36">
-        <v>26.316</v>
+        <v>27.09</v>
       </c>
       <c r="G36">
         <v>41.4</v>
@@ -4233,28 +4233,28 @@
         <v>16</v>
       </c>
       <c r="M36">
-        <v>1.3631688</v>
+        <v>1.403262</v>
       </c>
       <c r="N36">
-        <v>14.6368312</v>
+        <v>14.596738</v>
       </c>
       <c r="O36">
-        <v>3.93145286032</v>
+        <v>3.9206838268</v>
       </c>
       <c r="P36">
-        <v>10.70537833968</v>
+        <v>10.6760541732</v>
       </c>
       <c r="Q36">
-        <v>12.20537833968</v>
+        <v>12.1760541732</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1097523406118102</v>
+        <v>0.1105442746061133</v>
       </c>
       <c r="T36">
-        <v>1.246550152953164</v>
+        <v>1.2619864205281</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>11.73735783858903</v>
+        <v>11.40200475748649</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08511406049397362</v>
+        <v>0.08491015938415256</v>
       </c>
       <c r="C37">
-        <v>51.17649150912942</v>
+        <v>50.43126536673131</v>
       </c>
       <c r="D37">
-        <v>36.86649150912942</v>
+        <v>36.89526536673131</v>
       </c>
       <c r="E37">
-        <v>21.49</v>
+        <v>22.264</v>
       </c>
       <c r="F37">
-        <v>27.09</v>
+        <v>27.864</v>
       </c>
       <c r="G37">
         <v>41.4</v>
@@ -4315,28 +4315,28 @@
         <v>16</v>
       </c>
       <c r="M37">
-        <v>1.403262</v>
+        <v>1.4433552</v>
       </c>
       <c r="N37">
-        <v>14.596738</v>
+        <v>14.5566448</v>
       </c>
       <c r="O37">
-        <v>3.9206838268</v>
+        <v>3.90991479328</v>
       </c>
       <c r="P37">
-        <v>10.6760541732</v>
+        <v>10.64673000672</v>
       </c>
       <c r="Q37">
-        <v>12.1760541732</v>
+        <v>12.14673000672</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1105442746061133</v>
+        <v>0.1113609565377384</v>
       </c>
       <c r="T37">
-        <v>1.2619864205281</v>
+        <v>1.277905071464753</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>11.40200475748649</v>
+        <v>11.08528240311186</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08491015938415253</v>
+        <v>0.08470625827433145</v>
       </c>
       <c r="C38">
-        <v>50.43126536673132</v>
+        <v>49.68608417472286</v>
       </c>
       <c r="D38">
-        <v>36.89526536673132</v>
+        <v>36.92408417472286</v>
       </c>
       <c r="E38">
-        <v>22.264</v>
+        <v>23.038</v>
       </c>
       <c r="F38">
-        <v>27.864</v>
+        <v>28.638</v>
       </c>
       <c r="G38">
         <v>41.4</v>
@@ -4397,28 +4397,28 @@
         <v>16</v>
       </c>
       <c r="M38">
-        <v>1.4433552</v>
+        <v>1.4834484</v>
       </c>
       <c r="N38">
-        <v>14.5566448</v>
+        <v>14.5165516</v>
       </c>
       <c r="O38">
-        <v>3.90991479328</v>
+        <v>3.89914575976</v>
       </c>
       <c r="P38">
-        <v>10.64673000672</v>
+        <v>10.61740584024</v>
       </c>
       <c r="Q38">
-        <v>12.14673000672</v>
+        <v>12.11740584024</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1113609565377383</v>
+        <v>0.1122035648798912</v>
       </c>
       <c r="T38">
-        <v>1.277905071464752</v>
+        <v>1.294329076399394</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>11.08528240311186</v>
+        <v>10.78568017600073</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08470625827433145</v>
+        <v>0.08450235716451034</v>
       </c>
       <c r="C39">
-        <v>49.68608417472286</v>
+        <v>48.94094803851836</v>
       </c>
       <c r="D39">
-        <v>36.92408417472286</v>
+        <v>36.95294803851836</v>
       </c>
       <c r="E39">
-        <v>23.038</v>
+        <v>23.812</v>
       </c>
       <c r="F39">
-        <v>28.638</v>
+        <v>29.412</v>
       </c>
       <c r="G39">
         <v>41.4</v>
@@ -4479,28 +4479,28 @@
         <v>16</v>
       </c>
       <c r="M39">
-        <v>1.4834484</v>
+        <v>1.5235416</v>
       </c>
       <c r="N39">
-        <v>14.5165516</v>
+        <v>14.4764584</v>
       </c>
       <c r="O39">
-        <v>3.89914575976</v>
+        <v>3.88837672624</v>
       </c>
       <c r="P39">
-        <v>10.61740584024</v>
+        <v>10.58808167376</v>
       </c>
       <c r="Q39">
-        <v>12.11740584024</v>
+        <v>12.08808167376</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1122035648798912</v>
+        <v>0.113073354136307</v>
       </c>
       <c r="T39">
-        <v>1.294329076399394</v>
+        <v>1.31128288794483</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>10.78568017600073</v>
+        <v>10.50184648715861</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08450235716451034</v>
+        <v>0.08429845605468925</v>
       </c>
       <c r="C40">
-        <v>48.94094803851836</v>
+        <v>48.19585706386194</v>
       </c>
       <c r="D40">
-        <v>36.95294803851836</v>
+        <v>36.98185706386194</v>
       </c>
       <c r="E40">
-        <v>23.812</v>
+        <v>24.586</v>
       </c>
       <c r="F40">
-        <v>29.412</v>
+        <v>30.186</v>
       </c>
       <c r="G40">
         <v>41.4</v>
@@ -4561,28 +4561,28 @@
         <v>16</v>
       </c>
       <c r="M40">
-        <v>1.5235416</v>
+        <v>1.5636348</v>
       </c>
       <c r="N40">
-        <v>14.4764584</v>
+        <v>14.4363652</v>
       </c>
       <c r="O40">
-        <v>3.88837672624</v>
+        <v>3.87760769272</v>
       </c>
       <c r="P40">
-        <v>10.58808167376</v>
+        <v>10.55875750728</v>
       </c>
       <c r="Q40">
-        <v>12.08808167376</v>
+        <v>12.05875750728</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.113073354136307</v>
+        <v>0.1139716610732611</v>
       </c>
       <c r="T40">
-        <v>1.31128288794483</v>
+        <v>1.328792562163887</v>
       </c>
       <c r="U40">
         <v>0.0518</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>10.50184648715861</v>
+        <v>10.23256837210326</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08429845605468925</v>
+        <v>0.08409455494486816</v>
       </c>
       <c r="C41">
-        <v>48.19585706386194</v>
+        <v>47.45081135682894</v>
       </c>
       <c r="D41">
-        <v>36.98185706386194</v>
+        <v>37.01081135682893</v>
       </c>
       <c r="E41">
-        <v>24.586</v>
+        <v>25.36</v>
       </c>
       <c r="F41">
-        <v>30.186</v>
+        <v>30.96</v>
       </c>
       <c r="G41">
         <v>41.4</v>
@@ -4643,28 +4643,28 @@
         <v>16</v>
       </c>
       <c r="M41">
-        <v>1.5636348</v>
+        <v>1.603728</v>
       </c>
       <c r="N41">
-        <v>14.4363652</v>
+        <v>14.396272</v>
       </c>
       <c r="O41">
-        <v>3.87760769272</v>
+        <v>3.8668386592</v>
       </c>
       <c r="P41">
-        <v>10.55875750728</v>
+        <v>10.5294333408</v>
       </c>
       <c r="Q41">
-        <v>12.05875750728</v>
+        <v>12.0294333408</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1139716610732611</v>
+        <v>0.1148999115747803</v>
       </c>
       <c r="T41">
-        <v>1.328792562163887</v>
+        <v>1.346885892190246</v>
       </c>
       <c r="U41">
         <v>0.0518</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>10.23256837210326</v>
+        <v>9.976754162800676</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08409455494486816</v>
+        <v>0.08440043963504708</v>
       </c>
       <c r="C42">
-        <v>47.45081135682894</v>
+        <v>46.63339221704008</v>
       </c>
       <c r="D42">
-        <v>37.01081135682893</v>
+        <v>36.96739221704009</v>
       </c>
       <c r="E42">
-        <v>25.36</v>
+        <v>26.134</v>
       </c>
       <c r="F42">
-        <v>30.96</v>
+        <v>31.734</v>
       </c>
       <c r="G42">
         <v>41.4</v>
@@ -4725,45 +4725,45 @@
         <v>16</v>
       </c>
       <c r="M42">
-        <v>1.603728</v>
+        <v>1.697769</v>
       </c>
       <c r="N42">
-        <v>14.396272</v>
+        <v>14.302231</v>
       </c>
       <c r="O42">
-        <v>3.8668386592</v>
+        <v>3.8415792466</v>
       </c>
       <c r="P42">
-        <v>10.5294333408</v>
+        <v>10.4606517534</v>
       </c>
       <c r="Q42">
-        <v>12.0294333408</v>
+        <v>11.9606517534</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1148999115747803</v>
+        <v>0.115859628194995</v>
       </c>
       <c r="T42">
-        <v>1.346885892190246</v>
+        <v>1.365592555437838</v>
       </c>
       <c r="U42">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V42">
         <v>0.2686</v>
       </c>
       <c r="W42">
-        <v>0.03788652</v>
+        <v>0.0391299</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>9.976754162800676</v>
+        <v>9.424132493878732</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08440043963504708</v>
+        <v>0.08420897232522598</v>
       </c>
       <c r="C43">
-        <v>46.63339221704008</v>
+        <v>45.88655832050915</v>
       </c>
       <c r="D43">
-        <v>36.96739221704009</v>
+        <v>36.99455832050915</v>
       </c>
       <c r="E43">
-        <v>26.134</v>
+        <v>26.908</v>
       </c>
       <c r="F43">
-        <v>31.734</v>
+        <v>32.508</v>
       </c>
       <c r="G43">
         <v>41.4</v>
@@ -4807,28 +4807,28 @@
         <v>16</v>
       </c>
       <c r="M43">
-        <v>1.697769</v>
+        <v>1.739178</v>
       </c>
       <c r="N43">
-        <v>14.302231</v>
+        <v>14.260822</v>
       </c>
       <c r="O43">
-        <v>3.8415792466</v>
+        <v>3.8304567892</v>
       </c>
       <c r="P43">
-        <v>10.4606517534</v>
+        <v>10.4303652108</v>
       </c>
       <c r="Q43">
-        <v>11.9606517534</v>
+        <v>11.9303652108</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.115859628194995</v>
+        <v>0.1168524384917689</v>
       </c>
       <c r="T43">
-        <v>1.365592555437838</v>
+        <v>1.384944276038794</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>9.424132493878732</v>
+        <v>9.199748386881618</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08420897232522599</v>
+        <v>0.08401750501540489</v>
       </c>
       <c r="C44">
-        <v>45.88655832050915</v>
+        <v>45.13976438026735</v>
       </c>
       <c r="D44">
-        <v>36.99455832050915</v>
+        <v>37.02176438026735</v>
       </c>
       <c r="E44">
-        <v>26.90799999999999</v>
+        <v>27.682</v>
       </c>
       <c r="F44">
-        <v>32.508</v>
+        <v>33.282</v>
       </c>
       <c r="G44">
         <v>41.4</v>
@@ -4889,28 +4889,28 @@
         <v>16</v>
       </c>
       <c r="M44">
-        <v>1.739178</v>
+        <v>1.780587</v>
       </c>
       <c r="N44">
-        <v>14.260822</v>
+        <v>14.219413</v>
       </c>
       <c r="O44">
-        <v>3.8304567892</v>
+        <v>3.8193343318</v>
       </c>
       <c r="P44">
-        <v>10.4303652108</v>
+        <v>10.4000786682</v>
       </c>
       <c r="Q44">
-        <v>11.9303652108</v>
+        <v>11.9000786682</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1168524384917689</v>
+        <v>0.1178800842375524</v>
       </c>
       <c r="T44">
-        <v>1.384944276038794</v>
+        <v>1.404975004380135</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>9.199748386881621</v>
+        <v>8.985800749977397</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08401750501540489</v>
+        <v>0.08382603770558379</v>
       </c>
       <c r="C45">
-        <v>45.13976438026735</v>
+        <v>44.39301048453198</v>
       </c>
       <c r="D45">
-        <v>37.02176438026735</v>
+        <v>37.04901048453198</v>
       </c>
       <c r="E45">
-        <v>27.682</v>
+        <v>28.456</v>
       </c>
       <c r="F45">
-        <v>33.282</v>
+        <v>34.056</v>
       </c>
       <c r="G45">
         <v>41.4</v>
@@ -4971,28 +4971,28 @@
         <v>16</v>
       </c>
       <c r="M45">
-        <v>1.780587</v>
+        <v>1.821996</v>
       </c>
       <c r="N45">
-        <v>14.219413</v>
+        <v>14.178004</v>
       </c>
       <c r="O45">
-        <v>3.8193343318</v>
+        <v>3.8082118744</v>
       </c>
       <c r="P45">
-        <v>10.4000786682</v>
+        <v>10.3697921256</v>
       </c>
       <c r="Q45">
-        <v>11.9000786682</v>
+        <v>11.8697921256</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1178800842375524</v>
+        <v>0.1189444316171139</v>
       </c>
       <c r="T45">
-        <v>1.404975004380135</v>
+        <v>1.425721115876524</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>8.985800749977397</v>
+        <v>8.781578005659728</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08382603770558379</v>
+        <v>0.08363457039576269</v>
       </c>
       <c r="C46">
-        <v>44.39301048453198</v>
+        <v>43.6462967217802</v>
       </c>
       <c r="D46">
-        <v>37.04901048453198</v>
+        <v>37.0762967217802</v>
       </c>
       <c r="E46">
-        <v>28.456</v>
+        <v>29.23</v>
       </c>
       <c r="F46">
-        <v>34.056</v>
+        <v>34.83</v>
       </c>
       <c r="G46">
         <v>41.4</v>
@@ -5053,28 +5053,28 @@
         <v>16</v>
       </c>
       <c r="M46">
-        <v>1.821996</v>
+        <v>1.863405</v>
       </c>
       <c r="N46">
-        <v>14.178004</v>
+        <v>14.136595</v>
       </c>
       <c r="O46">
-        <v>3.8082118744</v>
+        <v>3.797089417</v>
       </c>
       <c r="P46">
-        <v>10.3697921256</v>
+        <v>10.339505583</v>
       </c>
       <c r="Q46">
-        <v>11.8697921256</v>
+        <v>11.839505583</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1189444316171139</v>
+        <v>0.1200474825377504</v>
       </c>
       <c r="T46">
-        <v>1.425721115876524</v>
+        <v>1.447221631427328</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>8.781578005659728</v>
+        <v>8.586431827756178</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08363457039576269</v>
+        <v>0.08344310308594161</v>
       </c>
       <c r="C47">
-        <v>43.6462967217802</v>
+        <v>42.89962318075004</v>
       </c>
       <c r="D47">
-        <v>37.0762967217802</v>
+        <v>37.10362318075004</v>
       </c>
       <c r="E47">
-        <v>29.23</v>
+        <v>30.004</v>
       </c>
       <c r="F47">
-        <v>34.83</v>
+        <v>35.604</v>
       </c>
       <c r="G47">
         <v>41.4</v>
@@ -5135,28 +5135,28 @@
         <v>16</v>
       </c>
       <c r="M47">
-        <v>1.863405</v>
+        <v>1.904814</v>
       </c>
       <c r="N47">
-        <v>14.136595</v>
+        <v>14.095186</v>
       </c>
       <c r="O47">
-        <v>3.797089417</v>
+        <v>3.7859669596</v>
       </c>
       <c r="P47">
-        <v>10.339505583</v>
+        <v>10.3092190404</v>
       </c>
       <c r="Q47">
-        <v>11.839505583</v>
+        <v>11.8092190404</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1200474825377504</v>
+        <v>0.1211913871961881</v>
       </c>
       <c r="T47">
-        <v>1.447221631427328</v>
+        <v>1.469518462368901</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>8.586431827756178</v>
+        <v>8.399770266283216</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08344310308594161</v>
+        <v>0.08325163577612052</v>
       </c>
       <c r="C48">
-        <v>42.89962318075004</v>
+        <v>42.15298995044131</v>
       </c>
       <c r="D48">
-        <v>37.10362318075004</v>
+        <v>37.13098995044131</v>
       </c>
       <c r="E48">
-        <v>30.004</v>
+        <v>30.778</v>
       </c>
       <c r="F48">
-        <v>35.604</v>
+        <v>36.378</v>
       </c>
       <c r="G48">
         <v>41.4</v>
@@ -5217,28 +5217,28 @@
         <v>16</v>
       </c>
       <c r="M48">
-        <v>1.904814</v>
+        <v>1.946223</v>
       </c>
       <c r="N48">
-        <v>14.095186</v>
+        <v>14.053777</v>
       </c>
       <c r="O48">
-        <v>3.7859669596</v>
+        <v>3.7748445022</v>
       </c>
       <c r="P48">
-        <v>10.3092190404</v>
+        <v>10.2789324978</v>
       </c>
       <c r="Q48">
-        <v>11.8092190404</v>
+        <v>11.7789324978</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1211913871961881</v>
+        <v>0.1223784580681519</v>
       </c>
       <c r="T48">
-        <v>1.469518462368901</v>
+        <v>1.492656683157327</v>
       </c>
       <c r="U48">
         <v>0.0535</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>8.399770266283216</v>
+        <v>8.221051749979319</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08325163577612052</v>
+        <v>0.08306016846629942</v>
       </c>
       <c r="C49">
-        <v>42.15298995044131</v>
+        <v>41.40639712011661</v>
       </c>
       <c r="D49">
-        <v>37.13098995044131</v>
+        <v>37.15839712011661</v>
       </c>
       <c r="E49">
-        <v>30.778</v>
+        <v>31.552</v>
       </c>
       <c r="F49">
-        <v>36.378</v>
+        <v>37.152</v>
       </c>
       <c r="G49">
         <v>41.4</v>
@@ -5299,28 +5299,28 @@
         <v>16</v>
       </c>
       <c r="M49">
-        <v>1.946223</v>
+        <v>1.987632</v>
       </c>
       <c r="N49">
-        <v>14.053777</v>
+        <v>14.012368</v>
       </c>
       <c r="O49">
-        <v>3.7748445022</v>
+        <v>3.7637220448</v>
       </c>
       <c r="P49">
-        <v>10.2789324978</v>
+        <v>10.2486459552</v>
       </c>
       <c r="Q49">
-        <v>11.7789324978</v>
+        <v>11.7486459552</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1223784580681519</v>
+        <v>0.1236111855121143</v>
       </c>
       <c r="T49">
-        <v>1.492656683157327</v>
+        <v>1.516684835514538</v>
       </c>
       <c r="U49">
         <v>0.0535</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>8.221051749979319</v>
+        <v>8.049779838521417</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08306016846629942</v>
+        <v>0.08286870115647832</v>
       </c>
       <c r="C50">
-        <v>41.40639712011662</v>
+        <v>40.65984477930225</v>
       </c>
       <c r="D50">
-        <v>37.15839712011661</v>
+        <v>37.18584477930226</v>
       </c>
       <c r="E50">
-        <v>31.55199999999999</v>
+        <v>32.32599999999999</v>
       </c>
       <c r="F50">
-        <v>37.15199999999999</v>
+        <v>37.92599999999999</v>
       </c>
       <c r="G50">
         <v>41.4</v>
@@ -5381,28 +5381,28 @@
         <v>16</v>
       </c>
       <c r="M50">
-        <v>1.987632</v>
+        <v>2.029041</v>
       </c>
       <c r="N50">
-        <v>14.012368</v>
+        <v>13.970959</v>
       </c>
       <c r="O50">
-        <v>3.7637220448</v>
+        <v>3.7525995874</v>
       </c>
       <c r="P50">
-        <v>10.2486459552</v>
+        <v>10.2183594126</v>
       </c>
       <c r="Q50">
-        <v>11.7486459552</v>
+        <v>11.7183594126</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1236111855121143</v>
+        <v>0.124892255208781</v>
       </c>
       <c r="T50">
-        <v>1.516684835514538</v>
+        <v>1.541655268356346</v>
       </c>
       <c r="U50">
         <v>0.0535</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>8.049779838521417</v>
+        <v>7.885498617327102</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08286870115647832</v>
+        <v>0.08267723384665722</v>
       </c>
       <c r="C51">
-        <v>40.65984477930225</v>
+        <v>39.91333301778932</v>
       </c>
       <c r="D51">
-        <v>37.18584477930226</v>
+        <v>37.21333301778932</v>
       </c>
       <c r="E51">
-        <v>32.32599999999999</v>
+        <v>33.09999999999999</v>
       </c>
       <c r="F51">
-        <v>37.92599999999999</v>
+        <v>38.7</v>
       </c>
       <c r="G51">
         <v>41.4</v>
@@ -5463,28 +5463,28 @@
         <v>16</v>
       </c>
       <c r="M51">
-        <v>2.029041</v>
+        <v>2.07045</v>
       </c>
       <c r="N51">
-        <v>13.970959</v>
+        <v>13.92955</v>
       </c>
       <c r="O51">
-        <v>3.7525995874</v>
+        <v>3.74147713</v>
       </c>
       <c r="P51">
-        <v>10.2183594126</v>
+        <v>10.18807287</v>
       </c>
       <c r="Q51">
-        <v>11.7183594126</v>
+        <v>11.68807287</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.124892255208781</v>
+        <v>0.1262245676933144</v>
       </c>
       <c r="T51">
-        <v>1.541655268356346</v>
+        <v>1.567624518511826</v>
       </c>
       <c r="U51">
         <v>0.0535</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>7.885498617327102</v>
+        <v>7.727788644980561</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08267723384665722</v>
+        <v>0.08278417773683613</v>
       </c>
       <c r="C52">
-        <v>39.91333301778932</v>
+        <v>39.12397447922168</v>
       </c>
       <c r="D52">
-        <v>37.21333301778932</v>
+        <v>37.19797447922168</v>
       </c>
       <c r="E52">
-        <v>33.09999999999999</v>
+        <v>33.874</v>
       </c>
       <c r="F52">
-        <v>38.7</v>
+        <v>39.474</v>
       </c>
       <c r="G52">
         <v>41.4</v>
@@ -5545,45 +5545,45 @@
         <v>16</v>
       </c>
       <c r="M52">
-        <v>2.07045</v>
+        <v>2.1434382</v>
       </c>
       <c r="N52">
-        <v>13.92955</v>
+        <v>13.8565618</v>
       </c>
       <c r="O52">
-        <v>3.74147713</v>
+        <v>3.72187249948</v>
       </c>
       <c r="P52">
-        <v>10.18807287</v>
+        <v>10.13468930052</v>
       </c>
       <c r="Q52">
-        <v>11.68807287</v>
+        <v>11.63468930052</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1262245676933144</v>
+        <v>0.1276112602792574</v>
       </c>
       <c r="T52">
-        <v>1.567624518511826</v>
+        <v>1.594653738061407</v>
       </c>
       <c r="U52">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V52">
         <v>0.2686</v>
       </c>
       <c r="W52">
-        <v>0.0391299</v>
+        <v>0.03971502</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y52">
-        <v>7.727788644980561</v>
+        <v>7.464642554191673</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08278417773683613</v>
+        <v>0.08259856162701504</v>
       </c>
       <c r="C53">
-        <v>39.12397447922168</v>
+        <v>38.37663947455243</v>
       </c>
       <c r="D53">
-        <v>37.19797447922168</v>
+        <v>37.22463947455243</v>
       </c>
       <c r="E53">
-        <v>33.874</v>
+        <v>34.648</v>
       </c>
       <c r="F53">
-        <v>39.474</v>
+        <v>40.248</v>
       </c>
       <c r="G53">
         <v>41.4</v>
@@ -5627,28 +5627,28 @@
         <v>16</v>
       </c>
       <c r="M53">
-        <v>2.1434382</v>
+        <v>2.1854664</v>
       </c>
       <c r="N53">
-        <v>13.8565618</v>
+        <v>13.8145336</v>
       </c>
       <c r="O53">
-        <v>3.72187249948</v>
+        <v>3.71058372496</v>
       </c>
       <c r="P53">
-        <v>10.13468930052</v>
+        <v>10.10394987504</v>
       </c>
       <c r="Q53">
-        <v>11.63468930052</v>
+        <v>11.60394987504</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1276112602792574</v>
+        <v>0.129055731722948</v>
       </c>
       <c r="T53">
-        <v>1.594653738061407</v>
+        <v>1.622809175092221</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>7.464642554191673</v>
+        <v>7.321091735841834</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08259856162701504</v>
+        <v>0.08241294551719394</v>
       </c>
       <c r="C54">
-        <v>38.37663947455243</v>
+        <v>37.62934272637647</v>
       </c>
       <c r="D54">
-        <v>37.22463947455243</v>
+        <v>37.25134272637646</v>
       </c>
       <c r="E54">
-        <v>34.648</v>
+        <v>35.422</v>
       </c>
       <c r="F54">
-        <v>40.248</v>
+        <v>41.022</v>
       </c>
       <c r="G54">
         <v>41.4</v>
@@ -5709,28 +5709,28 @@
         <v>16</v>
       </c>
       <c r="M54">
-        <v>2.1854664</v>
+        <v>2.2274946</v>
       </c>
       <c r="N54">
-        <v>13.8145336</v>
+        <v>13.7725054</v>
       </c>
       <c r="O54">
-        <v>3.71058372496</v>
+        <v>3.69929495044</v>
       </c>
       <c r="P54">
-        <v>10.10394987504</v>
+        <v>10.07321044956</v>
       </c>
       <c r="Q54">
-        <v>11.60394987504</v>
+        <v>11.57321044956</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.129055731722948</v>
+        <v>0.1305616700365829</v>
       </c>
       <c r="T54">
-        <v>1.622809175092221</v>
+        <v>1.652162715826474</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>7.321091735841834</v>
+        <v>7.182957929505194</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08241294551719394</v>
+        <v>0.08222732940737283</v>
       </c>
       <c r="C55">
-        <v>37.62934272637647</v>
+        <v>36.88208431708328</v>
       </c>
       <c r="D55">
-        <v>37.25134272637646</v>
+        <v>37.27808431708328</v>
       </c>
       <c r="E55">
-        <v>35.422</v>
+        <v>36.196</v>
       </c>
       <c r="F55">
-        <v>41.022</v>
+        <v>41.796</v>
       </c>
       <c r="G55">
         <v>41.4</v>
@@ -5791,28 +5791,28 @@
         <v>16</v>
       </c>
       <c r="M55">
-        <v>2.2274946</v>
+        <v>2.2695228</v>
       </c>
       <c r="N55">
-        <v>13.7725054</v>
+        <v>13.7304772</v>
       </c>
       <c r="O55">
-        <v>3.69929495044</v>
+        <v>3.68800617592</v>
       </c>
       <c r="P55">
-        <v>10.07321044956</v>
+        <v>10.04247102408</v>
       </c>
       <c r="Q55">
-        <v>11.57321044956</v>
+        <v>11.54247102408</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1305616700365829</v>
+        <v>0.1321330839290714</v>
       </c>
       <c r="T55">
-        <v>1.652162715826474</v>
+        <v>1.682792497462215</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>7.182957929505194</v>
+        <v>7.049940190069913</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08222732940737283</v>
+        <v>0.08204171329755175</v>
       </c>
       <c r="C56">
-        <v>36.88208431708328</v>
+        <v>36.13486432929907</v>
       </c>
       <c r="D56">
-        <v>37.27808431708328</v>
+        <v>37.30486432929907</v>
       </c>
       <c r="E56">
-        <v>36.196</v>
+        <v>36.97</v>
       </c>
       <c r="F56">
-        <v>41.796</v>
+        <v>42.57</v>
       </c>
       <c r="G56">
         <v>41.4</v>
@@ -5873,28 +5873,28 @@
         <v>16</v>
       </c>
       <c r="M56">
-        <v>2.2695228</v>
+        <v>2.311551</v>
       </c>
       <c r="N56">
-        <v>13.7304772</v>
+        <v>13.688449</v>
       </c>
       <c r="O56">
-        <v>3.68800617592</v>
+        <v>3.6767174014</v>
       </c>
       <c r="P56">
-        <v>10.04247102408</v>
+        <v>10.0117315986</v>
       </c>
       <c r="Q56">
-        <v>11.54247102408</v>
+        <v>11.5117315986</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1321330839290714</v>
+        <v>0.1337743384390039</v>
       </c>
       <c r="T56">
-        <v>1.682792497462215</v>
+        <v>1.714783602726212</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>7.049940190069913</v>
+        <v>6.921759459341368</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08204171329755175</v>
+        <v>0.08185609718773065</v>
       </c>
       <c r="C57">
-        <v>36.13486432929907</v>
+        <v>35.38768284588769</v>
       </c>
       <c r="D57">
-        <v>37.30486432929907</v>
+        <v>37.33168284588768</v>
       </c>
       <c r="E57">
-        <v>36.97</v>
+        <v>37.744</v>
       </c>
       <c r="F57">
-        <v>42.57</v>
+        <v>43.344</v>
       </c>
       <c r="G57">
         <v>41.4</v>
@@ -5955,28 +5955,28 @@
         <v>16</v>
       </c>
       <c r="M57">
-        <v>2.311551</v>
+        <v>2.3535792</v>
       </c>
       <c r="N57">
-        <v>13.688449</v>
+        <v>13.6464208</v>
       </c>
       <c r="O57">
-        <v>3.6767174014</v>
+        <v>3.66542862688</v>
       </c>
       <c r="P57">
-        <v>10.0117315986</v>
+        <v>9.980992173120001</v>
       </c>
       <c r="Q57">
-        <v>11.5117315986</v>
+        <v>11.48099217312</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1337743384390039</v>
+        <v>0.1354901954266606</v>
       </c>
       <c r="T57">
-        <v>1.714783602726212</v>
+        <v>1.748228849138573</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>6.921759459341368</v>
+        <v>6.79815661185313</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08185609718773065</v>
+        <v>0.08167048107790956</v>
       </c>
       <c r="C58">
-        <v>35.38768284588769</v>
+        <v>34.64053994995137</v>
       </c>
       <c r="D58">
-        <v>37.33168284588768</v>
+        <v>37.35853994995136</v>
       </c>
       <c r="E58">
-        <v>37.744</v>
+        <v>38.518</v>
       </c>
       <c r="F58">
-        <v>43.344</v>
+        <v>44.118</v>
       </c>
       <c r="G58">
         <v>41.4</v>
@@ -6037,28 +6037,28 @@
         <v>16</v>
       </c>
       <c r="M58">
-        <v>2.3535792</v>
+        <v>2.3956074</v>
       </c>
       <c r="N58">
-        <v>13.6464208</v>
+        <v>13.6043926</v>
       </c>
       <c r="O58">
-        <v>3.66542862688</v>
+        <v>3.65413985236</v>
       </c>
       <c r="P58">
-        <v>9.980992173120001</v>
+        <v>9.95025274764</v>
       </c>
       <c r="Q58">
-        <v>11.48099217312</v>
+        <v>11.45025274764</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1354901954266606</v>
+        <v>0.1372858597160687</v>
       </c>
       <c r="T58">
-        <v>1.748228849138573</v>
+        <v>1.783229688407322</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>6.79815661185313</v>
+        <v>6.678890706382022</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08167048107790956</v>
+        <v>0.08148486496808846</v>
       </c>
       <c r="C59">
-        <v>34.64053994995137</v>
+        <v>33.89343572483173</v>
       </c>
       <c r="D59">
-        <v>37.35853994995136</v>
+        <v>37.38543572483174</v>
       </c>
       <c r="E59">
-        <v>38.518</v>
+        <v>39.292</v>
       </c>
       <c r="F59">
-        <v>44.118</v>
+        <v>44.892</v>
       </c>
       <c r="G59">
         <v>41.4</v>
@@ -6119,28 +6119,28 @@
         <v>16</v>
       </c>
       <c r="M59">
-        <v>2.3956074</v>
+        <v>2.4376356</v>
       </c>
       <c r="N59">
-        <v>13.6043926</v>
+        <v>13.5623644</v>
       </c>
       <c r="O59">
-        <v>3.65413985236</v>
+        <v>3.64285107784</v>
       </c>
       <c r="P59">
-        <v>9.95025274764</v>
+        <v>9.91951332216</v>
       </c>
       <c r="Q59">
-        <v>11.45025274764</v>
+        <v>11.41951332216</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1372858597160687</v>
+        <v>0.1391670318287821</v>
       </c>
       <c r="T59">
-        <v>1.783229688407322</v>
+        <v>1.819897234307917</v>
       </c>
       <c r="U59">
         <v>0.0543</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>6.678890706382022</v>
+        <v>6.563737418340953</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08148486496808846</v>
+        <v>0.08129924885826736</v>
       </c>
       <c r="C60">
-        <v>33.89343572483174</v>
+        <v>33.14637025411054</v>
       </c>
       <c r="D60">
-        <v>37.38543572483174</v>
+        <v>37.41237025411054</v>
       </c>
       <c r="E60">
-        <v>39.29199999999999</v>
+        <v>40.06599999999999</v>
       </c>
       <c r="F60">
-        <v>44.89199999999999</v>
+        <v>45.66599999999999</v>
       </c>
       <c r="G60">
         <v>41.4</v>
@@ -6201,28 +6201,28 @@
         <v>16</v>
       </c>
       <c r="M60">
-        <v>2.437635599999999</v>
+        <v>2.4796638</v>
       </c>
       <c r="N60">
-        <v>13.5623644</v>
+        <v>13.5203362</v>
       </c>
       <c r="O60">
-        <v>3.64285107784</v>
+        <v>3.63156230332</v>
       </c>
       <c r="P60">
-        <v>9.91951332216</v>
+        <v>9.88877389668</v>
       </c>
       <c r="Q60">
-        <v>11.41951332216</v>
+        <v>11.38877389668</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.139167031828782</v>
+        <v>0.1411399684347985</v>
       </c>
       <c r="T60">
-        <v>1.819897234307917</v>
+        <v>1.85835344098415</v>
       </c>
       <c r="U60">
         <v>0.0543</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>6.563737418340954</v>
+        <v>6.452487631589412</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08129924885826736</v>
+        <v>0.08111363274844628</v>
       </c>
       <c r="C61">
-        <v>33.14637025411054</v>
+        <v>32.3993436216106</v>
       </c>
       <c r="D61">
-        <v>37.41237025411054</v>
+        <v>37.43934362161059</v>
       </c>
       <c r="E61">
-        <v>40.06599999999999</v>
+        <v>40.83999999999999</v>
       </c>
       <c r="F61">
-        <v>45.66599999999999</v>
+        <v>46.43999999999999</v>
       </c>
       <c r="G61">
         <v>41.4</v>
@@ -6283,28 +6283,28 @@
         <v>16</v>
       </c>
       <c r="M61">
-        <v>2.4796638</v>
+        <v>2.521691999999999</v>
       </c>
       <c r="N61">
-        <v>13.5203362</v>
+        <v>13.478308</v>
       </c>
       <c r="O61">
-        <v>3.63156230332</v>
+        <v>3.6202735288</v>
       </c>
       <c r="P61">
-        <v>9.88877389668</v>
+        <v>9.8580344712</v>
       </c>
       <c r="Q61">
-        <v>11.38877389668</v>
+        <v>11.3580344712</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1411399684347985</v>
+        <v>0.1432115518711157</v>
       </c>
       <c r="T61">
-        <v>1.85835344098415</v>
+        <v>1.898732457994196</v>
       </c>
       <c r="U61">
         <v>0.0543</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>6.452487631589412</v>
+        <v>6.344946171062922</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08111363274844628</v>
+        <v>0.08092801663862519</v>
       </c>
       <c r="C62">
-        <v>32.3993436216106</v>
+        <v>31.65235591139662</v>
       </c>
       <c r="D62">
-        <v>37.43934362161059</v>
+        <v>37.46635591139661</v>
       </c>
       <c r="E62">
-        <v>40.83999999999999</v>
+        <v>41.61399999999999</v>
       </c>
       <c r="F62">
-        <v>46.43999999999999</v>
+        <v>47.21399999999999</v>
       </c>
       <c r="G62">
         <v>41.4</v>
@@ -6365,28 +6365,28 @@
         <v>16</v>
       </c>
       <c r="M62">
-        <v>2.521691999999999</v>
+        <v>2.5637202</v>
       </c>
       <c r="N62">
-        <v>13.478308</v>
+        <v>13.4362798</v>
       </c>
       <c r="O62">
-        <v>3.6202735288</v>
+        <v>3.60898475428</v>
       </c>
       <c r="P62">
-        <v>9.8580344712</v>
+        <v>9.827295045720001</v>
       </c>
       <c r="Q62">
-        <v>11.3580344712</v>
+        <v>11.32729504572</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1432115518711157</v>
+        <v>0.1453893703554492</v>
       </c>
       <c r="T62">
-        <v>1.898732457994196</v>
+        <v>1.941182193825268</v>
       </c>
       <c r="U62">
         <v>0.0543</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>6.344946171062922</v>
+        <v>6.240930660061891</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08092801663862519</v>
+        <v>0.0807424005288041</v>
       </c>
       <c r="C63">
-        <v>31.65235591139662</v>
+        <v>30.90540720777611</v>
       </c>
       <c r="D63">
-        <v>37.46635591139661</v>
+        <v>37.4934072077761</v>
       </c>
       <c r="E63">
-        <v>41.61399999999999</v>
+        <v>42.38799999999999</v>
       </c>
       <c r="F63">
-        <v>47.21399999999999</v>
+        <v>47.98799999999999</v>
       </c>
       <c r="G63">
         <v>41.4</v>
@@ -6447,28 +6447,28 @@
         <v>16</v>
       </c>
       <c r="M63">
-        <v>2.5637202</v>
+        <v>2.6057484</v>
       </c>
       <c r="N63">
-        <v>13.4362798</v>
+        <v>13.3942516</v>
       </c>
       <c r="O63">
-        <v>3.60898475428</v>
+        <v>3.59769597976</v>
       </c>
       <c r="P63">
-        <v>9.827295045720001</v>
+        <v>9.796555620239999</v>
       </c>
       <c r="Q63">
-        <v>11.32729504572</v>
+        <v>11.29655562024</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1453893703554492</v>
+        <v>0.1476818108652739</v>
       </c>
       <c r="T63">
-        <v>1.941182193825268</v>
+        <v>1.98586612627903</v>
       </c>
       <c r="U63">
         <v>0.0543</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>6.240930660061891</v>
+        <v>6.140270488125409</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.0807424005288041</v>
+        <v>0.08101756641898299</v>
       </c>
       <c r="C64">
-        <v>30.90540720777611</v>
+        <v>30.09131907117203</v>
       </c>
       <c r="D64">
-        <v>37.4934072077761</v>
+        <v>37.45331907117202</v>
       </c>
       <c r="E64">
-        <v>42.38799999999999</v>
+        <v>43.16199999999999</v>
       </c>
       <c r="F64">
-        <v>47.98799999999999</v>
+        <v>48.76199999999999</v>
       </c>
       <c r="G64">
         <v>41.4</v>
@@ -6529,45 +6529,45 @@
         <v>16</v>
       </c>
       <c r="M64">
-        <v>2.6057484</v>
+        <v>2.6965386</v>
       </c>
       <c r="N64">
-        <v>13.3942516</v>
+        <v>13.3034614</v>
       </c>
       <c r="O64">
-        <v>3.59769597976</v>
+        <v>3.57330973204</v>
       </c>
       <c r="P64">
-        <v>9.796555620239999</v>
+        <v>9.73015166796</v>
       </c>
       <c r="Q64">
-        <v>11.29655562024</v>
+        <v>11.23015166796</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1476818108652739</v>
+        <v>0.1500981670783324</v>
       </c>
       <c r="T64">
-        <v>1.98586612627903</v>
+        <v>2.032965406432994</v>
       </c>
       <c r="U64">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V64">
         <v>0.2686</v>
       </c>
       <c r="W64">
-        <v>0.03971502</v>
+        <v>0.04044642</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y64">
-        <v>6.140270488125409</v>
+        <v>5.933532714866385</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08101756641898299</v>
+        <v>0.08083926430916191</v>
       </c>
       <c r="C65">
-        <v>30.09131907117203</v>
+        <v>29.34328561509601</v>
       </c>
       <c r="D65">
-        <v>37.45331907117202</v>
+        <v>37.47928561509601</v>
       </c>
       <c r="E65">
-        <v>43.16199999999999</v>
+        <v>43.93599999999999</v>
       </c>
       <c r="F65">
-        <v>48.76199999999999</v>
+        <v>49.53599999999999</v>
       </c>
       <c r="G65">
         <v>41.4</v>
@@ -6611,28 +6611,28 @@
         <v>16</v>
       </c>
       <c r="M65">
-        <v>2.6965386</v>
+        <v>2.7393408</v>
       </c>
       <c r="N65">
-        <v>13.3034614</v>
+        <v>13.2606592</v>
       </c>
       <c r="O65">
-        <v>3.57330973204</v>
+        <v>3.56181306112</v>
       </c>
       <c r="P65">
-        <v>9.73015166796</v>
+        <v>9.698846138879999</v>
       </c>
       <c r="Q65">
-        <v>11.23015166796</v>
+        <v>11.19884613888</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1500981670783324</v>
+        <v>0.1526487653032275</v>
       </c>
       <c r="T65">
-        <v>2.032965406432994</v>
+        <v>2.082681313262179</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.933532714866385</v>
+        <v>5.840821266196597</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08083926430916191</v>
+        <v>0.08066096219934081</v>
       </c>
       <c r="C66">
-        <v>29.34328561509601</v>
+        <v>28.59528818942866</v>
       </c>
       <c r="D66">
-        <v>37.47928561509601</v>
+        <v>37.50528818942867</v>
       </c>
       <c r="E66">
-        <v>43.93599999999999</v>
+        <v>44.70999999999999</v>
       </c>
       <c r="F66">
-        <v>49.53599999999999</v>
+        <v>50.31</v>
       </c>
       <c r="G66">
         <v>41.4</v>
@@ -6693,28 +6693,28 @@
         <v>16</v>
       </c>
       <c r="M66">
-        <v>2.7393408</v>
+        <v>2.782143</v>
       </c>
       <c r="N66">
-        <v>13.2606592</v>
+        <v>13.217857</v>
       </c>
       <c r="O66">
-        <v>3.56181306112</v>
+        <v>3.5503163902</v>
       </c>
       <c r="P66">
-        <v>9.698846138879999</v>
+        <v>9.6675406098</v>
       </c>
       <c r="Q66">
-        <v>11.19884613888</v>
+        <v>11.1675406098</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1526487653032275</v>
+        <v>0.1553451119981166</v>
       </c>
       <c r="T66">
-        <v>2.082681313262179</v>
+        <v>2.135238129053031</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.840821266196597</v>
+        <v>5.750962477485881</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08066096219934081</v>
+        <v>0.08048266008951971</v>
       </c>
       <c r="C67">
-        <v>28.59528818942866</v>
+        <v>27.84732686921415</v>
       </c>
       <c r="D67">
-        <v>37.50528818942867</v>
+        <v>37.53132686921415</v>
       </c>
       <c r="E67">
-        <v>44.70999999999999</v>
+        <v>45.48399999999999</v>
       </c>
       <c r="F67">
-        <v>50.31</v>
+        <v>51.084</v>
       </c>
       <c r="G67">
         <v>41.4</v>
@@ -6775,28 +6775,28 @@
         <v>16</v>
       </c>
       <c r="M67">
-        <v>2.782143</v>
+        <v>2.8249452</v>
       </c>
       <c r="N67">
-        <v>13.217857</v>
+        <v>13.1750548</v>
       </c>
       <c r="O67">
-        <v>3.5503163902</v>
+        <v>3.53881971928</v>
       </c>
       <c r="P67">
-        <v>9.6675406098</v>
+        <v>9.636235080719999</v>
       </c>
       <c r="Q67">
-        <v>11.1675406098</v>
+        <v>11.13623508072</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1553451119981166</v>
+        <v>0.1582000673221168</v>
       </c>
       <c r="T67">
-        <v>2.135238129053031</v>
+        <v>2.190886522243345</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.750962477485881</v>
+        <v>5.663826682372458</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08048266008951971</v>
+        <v>0.08030435797969862</v>
       </c>
       <c r="C68">
-        <v>27.84732686921415</v>
+        <v>27.09940172970516</v>
       </c>
       <c r="D68">
-        <v>37.53132686921415</v>
+        <v>37.55740172970516</v>
       </c>
       <c r="E68">
-        <v>45.48399999999999</v>
+        <v>46.258</v>
       </c>
       <c r="F68">
-        <v>51.084</v>
+        <v>51.858</v>
       </c>
       <c r="G68">
         <v>41.4</v>
@@ -6857,28 +6857,28 @@
         <v>16</v>
       </c>
       <c r="M68">
-        <v>2.8249452</v>
+        <v>2.8677474</v>
       </c>
       <c r="N68">
-        <v>13.1750548</v>
+        <v>13.1322526</v>
       </c>
       <c r="O68">
-        <v>3.53881971928</v>
+        <v>3.52732304836</v>
       </c>
       <c r="P68">
-        <v>9.636235080719999</v>
+        <v>9.604929551640002</v>
       </c>
       <c r="Q68">
-        <v>11.13623508072</v>
+        <v>11.10492955164</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1582000673221168</v>
+        <v>0.161228050241511</v>
       </c>
       <c r="T68">
-        <v>2.190886522243345</v>
+        <v>2.249907545323982</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.663826682372458</v>
+        <v>5.579291955769885</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08030435797969862</v>
+        <v>0.08012605586987753</v>
       </c>
       <c r="C69">
-        <v>27.09940172970516</v>
+        <v>26.35151284636368</v>
       </c>
       <c r="D69">
-        <v>37.55740172970516</v>
+        <v>37.58351284636367</v>
       </c>
       <c r="E69">
-        <v>46.258</v>
+        <v>47.032</v>
       </c>
       <c r="F69">
-        <v>51.858</v>
+        <v>52.632</v>
       </c>
       <c r="G69">
         <v>41.4</v>
@@ -6939,28 +6939,28 @@
         <v>16</v>
       </c>
       <c r="M69">
-        <v>2.8677474</v>
+        <v>2.9105496</v>
       </c>
       <c r="N69">
-        <v>13.1322526</v>
+        <v>13.0894504</v>
       </c>
       <c r="O69">
-        <v>3.52732304836</v>
+        <v>3.51582637744</v>
       </c>
       <c r="P69">
-        <v>9.604929551640002</v>
+        <v>9.573624022560001</v>
       </c>
       <c r="Q69">
-        <v>11.10492955164</v>
+        <v>11.07362402256</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.161228050241511</v>
+        <v>0.1644452820933673</v>
       </c>
       <c r="T69">
-        <v>2.249907545323982</v>
+        <v>2.312617382347158</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.579291955769885</v>
+        <v>5.497243544655621</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08012605586987753</v>
+        <v>0.07994775376005643</v>
       </c>
       <c r="C70">
-        <v>26.35151284636368</v>
+        <v>25.60366029486168</v>
       </c>
       <c r="D70">
-        <v>37.58351284636367</v>
+        <v>37.60966029486168</v>
       </c>
       <c r="E70">
-        <v>47.032</v>
+        <v>47.806</v>
       </c>
       <c r="F70">
-        <v>52.632</v>
+        <v>53.406</v>
       </c>
       <c r="G70">
         <v>41.4</v>
@@ -7021,28 +7021,28 @@
         <v>16</v>
       </c>
       <c r="M70">
-        <v>2.9105496</v>
+        <v>2.9533518</v>
       </c>
       <c r="N70">
-        <v>13.0894504</v>
+        <v>13.0466482</v>
       </c>
       <c r="O70">
-        <v>3.51582637744</v>
+        <v>3.50432970652</v>
       </c>
       <c r="P70">
-        <v>9.573624022560001</v>
+        <v>9.54231849348</v>
       </c>
       <c r="Q70">
-        <v>11.07362402256</v>
+        <v>11.04231849348</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1644452820933673</v>
+        <v>0.1678700772905046</v>
       </c>
       <c r="T70">
-        <v>2.312617382347158</v>
+        <v>2.379373015307313</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.497243544655621</v>
+        <v>5.417573348356264</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07994775376005643</v>
+        <v>0.07976945165023534</v>
       </c>
       <c r="C71">
-        <v>25.60366029486168</v>
+        <v>24.85584415108188</v>
       </c>
       <c r="D71">
-        <v>37.60966029486168</v>
+        <v>37.63584415108188</v>
       </c>
       <c r="E71">
-        <v>47.806</v>
+        <v>48.58</v>
       </c>
       <c r="F71">
-        <v>53.406</v>
+        <v>54.18</v>
       </c>
       <c r="G71">
         <v>41.4</v>
@@ -7103,28 +7103,28 @@
         <v>16</v>
       </c>
       <c r="M71">
-        <v>2.9533518</v>
+        <v>2.996154</v>
       </c>
       <c r="N71">
-        <v>13.0466482</v>
+        <v>13.003846</v>
       </c>
       <c r="O71">
-        <v>3.50432970652</v>
+        <v>3.4928330356</v>
       </c>
       <c r="P71">
-        <v>9.54231849348</v>
+        <v>9.511012964399999</v>
       </c>
       <c r="Q71">
-        <v>11.04231849348</v>
+        <v>11.0110129644</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1678700772905046</v>
+        <v>0.1715231921674512</v>
       </c>
       <c r="T71">
-        <v>2.379373015307313</v>
+        <v>2.450579023798146</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.417573348356264</v>
+        <v>5.340179443379745</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07976945165023534</v>
+        <v>0.07959114954041424</v>
       </c>
       <c r="C72">
-        <v>24.85584415108188</v>
+        <v>24.10806449111846</v>
       </c>
       <c r="D72">
-        <v>37.63584415108188</v>
+        <v>37.66206449111846</v>
       </c>
       <c r="E72">
-        <v>48.58</v>
+        <v>49.354</v>
       </c>
       <c r="F72">
-        <v>54.18</v>
+        <v>54.954</v>
       </c>
       <c r="G72">
         <v>41.4</v>
@@ -7185,28 +7185,28 @@
         <v>16</v>
       </c>
       <c r="M72">
-        <v>2.996154</v>
+        <v>3.0389562</v>
       </c>
       <c r="N72">
-        <v>13.003846</v>
+        <v>12.9610438</v>
       </c>
       <c r="O72">
-        <v>3.4928330356</v>
+        <v>3.48133636468</v>
       </c>
       <c r="P72">
-        <v>9.511012964399999</v>
+        <v>9.479707435319998</v>
       </c>
       <c r="Q72">
-        <v>11.0110129644</v>
+        <v>10.97970743532</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1715231921674512</v>
+        <v>0.1754282460014285</v>
       </c>
       <c r="T72">
-        <v>2.450579023798146</v>
+        <v>2.526695791495242</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.340179443379745</v>
+        <v>5.264965648402566</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07959114954041425</v>
+        <v>0.07941284743059315</v>
       </c>
       <c r="C73">
-        <v>24.10806449111847</v>
+        <v>23.36032139127779</v>
       </c>
       <c r="D73">
-        <v>37.66206449111846</v>
+        <v>37.68832139127779</v>
       </c>
       <c r="E73">
-        <v>49.35399999999999</v>
+        <v>50.12799999999999</v>
       </c>
       <c r="F73">
-        <v>54.95399999999999</v>
+        <v>55.72799999999999</v>
       </c>
       <c r="G73">
         <v>41.4</v>
@@ -7267,28 +7267,28 @@
         <v>16</v>
       </c>
       <c r="M73">
-        <v>3.0389562</v>
+        <v>3.0817584</v>
       </c>
       <c r="N73">
-        <v>12.9610438</v>
+        <v>12.9182416</v>
       </c>
       <c r="O73">
-        <v>3.48133636468</v>
+        <v>3.46983969376</v>
       </c>
       <c r="P73">
-        <v>9.47970743532</v>
+        <v>9.448401906240001</v>
       </c>
       <c r="Q73">
-        <v>10.97970743532</v>
+        <v>10.94840190624</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1754282460014284</v>
+        <v>0.1796122322521184</v>
       </c>
       <c r="T73">
-        <v>2.526695791495241</v>
+        <v>2.608249471170701</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>5.264965648402567</v>
+        <v>5.191841125508087</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07941284743059315</v>
+        <v>0.07923454532077207</v>
       </c>
       <c r="C74">
-        <v>23.36032139127779</v>
+        <v>22.6126149280792</v>
       </c>
       <c r="D74">
-        <v>37.68832139127779</v>
+        <v>37.7146149280792</v>
       </c>
       <c r="E74">
-        <v>50.12799999999999</v>
+        <v>50.90199999999999</v>
       </c>
       <c r="F74">
-        <v>55.72799999999999</v>
+        <v>56.502</v>
       </c>
       <c r="G74">
         <v>41.4</v>
@@ -7349,28 +7349,28 @@
         <v>16</v>
       </c>
       <c r="M74">
-        <v>3.0817584</v>
+        <v>3.1245606</v>
       </c>
       <c r="N74">
-        <v>12.9182416</v>
+        <v>12.8754394</v>
       </c>
       <c r="O74">
-        <v>3.46983969376</v>
+        <v>3.45834302284</v>
       </c>
       <c r="P74">
-        <v>9.448401906240001</v>
+        <v>9.41709637716</v>
       </c>
       <c r="Q74">
-        <v>10.94840190624</v>
+        <v>10.91709637716</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1796122322521184</v>
+        <v>0.1841061434102669</v>
       </c>
       <c r="T74">
-        <v>2.608249471170701</v>
+        <v>2.695844164155456</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>5.191841125508087</v>
+        <v>5.120720014199757</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07923454532077207</v>
+        <v>0.07905624321095096</v>
       </c>
       <c r="C75">
-        <v>22.6126149280792</v>
+        <v>21.8649451782557</v>
       </c>
       <c r="D75">
-        <v>37.7146149280792</v>
+        <v>37.74094517825569</v>
       </c>
       <c r="E75">
-        <v>50.90199999999999</v>
+        <v>51.67599999999999</v>
       </c>
       <c r="F75">
-        <v>56.502</v>
+        <v>57.276</v>
       </c>
       <c r="G75">
         <v>41.4</v>
@@ -7431,28 +7431,28 @@
         <v>16</v>
       </c>
       <c r="M75">
-        <v>3.1245606</v>
+        <v>3.1673628</v>
       </c>
       <c r="N75">
-        <v>12.8754394</v>
+        <v>12.8326372</v>
       </c>
       <c r="O75">
-        <v>3.45834302284</v>
+        <v>3.44684635192</v>
       </c>
       <c r="P75">
-        <v>9.41709637716</v>
+        <v>9.385790848080001</v>
       </c>
       <c r="Q75">
-        <v>10.91709637716</v>
+        <v>10.88579084808</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1841061434102669</v>
+        <v>0.1889457400421191</v>
       </c>
       <c r="T75">
-        <v>2.695844164155456</v>
+        <v>2.790176910446728</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>5.120720014199757</v>
+        <v>5.051521095088949</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07905624321095096</v>
+        <v>0.07887794110112986</v>
       </c>
       <c r="C76">
-        <v>21.8649451782557</v>
+        <v>21.11731221875472</v>
       </c>
       <c r="D76">
-        <v>37.74094517825569</v>
+        <v>37.76731221875471</v>
       </c>
       <c r="E76">
-        <v>51.67599999999999</v>
+        <v>52.45</v>
       </c>
       <c r="F76">
-        <v>57.276</v>
+        <v>58.05</v>
       </c>
       <c r="G76">
         <v>41.4</v>
@@ -7513,28 +7513,28 @@
         <v>16</v>
       </c>
       <c r="M76">
-        <v>3.1673628</v>
+        <v>3.210165</v>
       </c>
       <c r="N76">
-        <v>12.8326372</v>
+        <v>12.789835</v>
       </c>
       <c r="O76">
-        <v>3.44684635192</v>
+        <v>3.435349681</v>
       </c>
       <c r="P76">
-        <v>9.385790848080001</v>
+        <v>9.354485319</v>
       </c>
       <c r="Q76">
-        <v>10.88579084808</v>
+        <v>10.854485319</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1889457400421191</v>
+        <v>0.1941725044045195</v>
       </c>
       <c r="T76">
-        <v>2.790176910446728</v>
+        <v>2.892056276441304</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>5.051521095088949</v>
+        <v>4.984167480487763</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07887794110112986</v>
+        <v>0.07869963899130877</v>
       </c>
       <c r="C77">
-        <v>21.11731221875472</v>
+        <v>20.36971612673889</v>
       </c>
       <c r="D77">
-        <v>37.76731221875471</v>
+        <v>37.79371612673887</v>
       </c>
       <c r="E77">
-        <v>52.45</v>
+        <v>53.22399999999999</v>
       </c>
       <c r="F77">
-        <v>58.05</v>
+        <v>58.82399999999999</v>
       </c>
       <c r="G77">
         <v>41.4</v>
@@ -7595,28 +7595,28 @@
         <v>16</v>
       </c>
       <c r="M77">
-        <v>3.210165</v>
+        <v>3.2529672</v>
       </c>
       <c r="N77">
-        <v>12.789835</v>
+        <v>12.7470328</v>
       </c>
       <c r="O77">
-        <v>3.435349681</v>
+        <v>3.42385301008</v>
       </c>
       <c r="P77">
-        <v>9.354485319</v>
+        <v>9.323179789919999</v>
       </c>
       <c r="Q77">
-        <v>10.854485319</v>
+        <v>10.82317978992</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1941725044045195</v>
+        <v>0.1998348324637866</v>
       </c>
       <c r="T77">
-        <v>2.892056276441304</v>
+        <v>3.002425589602094</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.984167480487763</v>
+        <v>4.918586329428714</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07869963899130877</v>
+        <v>0.07852133688148767</v>
       </c>
       <c r="C78">
-        <v>20.36971612673889</v>
+        <v>19.62215697958674</v>
       </c>
       <c r="D78">
-        <v>37.79371612673887</v>
+        <v>37.82015697958674</v>
       </c>
       <c r="E78">
-        <v>53.22399999999999</v>
+        <v>53.99799999999999</v>
       </c>
       <c r="F78">
-        <v>58.82399999999999</v>
+        <v>59.59799999999999</v>
       </c>
       <c r="G78">
         <v>41.4</v>
@@ -7677,28 +7677,28 @@
         <v>16</v>
       </c>
       <c r="M78">
-        <v>3.2529672</v>
+        <v>3.2957694</v>
       </c>
       <c r="N78">
-        <v>12.7470328</v>
+        <v>12.7042306</v>
       </c>
       <c r="O78">
-        <v>3.42385301008</v>
+        <v>3.41235633916</v>
       </c>
       <c r="P78">
-        <v>9.323179789919999</v>
+        <v>9.29187426084</v>
       </c>
       <c r="Q78">
-        <v>10.82317978992</v>
+        <v>10.79187426084</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1998348324637866</v>
+        <v>0.2059895368760334</v>
       </c>
       <c r="T78">
-        <v>3.002425589602094</v>
+        <v>3.122392234342083</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.918586329428714</v>
+        <v>4.854708584890679</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07852133688148767</v>
+        <v>0.07834303477166657</v>
       </c>
       <c r="C79">
-        <v>19.62215697958674</v>
+        <v>18.87463485489356</v>
       </c>
       <c r="D79">
-        <v>37.82015697958674</v>
+        <v>37.84663485489357</v>
       </c>
       <c r="E79">
-        <v>53.99799999999999</v>
+        <v>54.77199999999999</v>
       </c>
       <c r="F79">
-        <v>59.59799999999999</v>
+        <v>60.37199999999999</v>
       </c>
       <c r="G79">
         <v>41.4</v>
@@ -7759,28 +7759,28 @@
         <v>16</v>
       </c>
       <c r="M79">
-        <v>3.2957694</v>
+        <v>3.3385716</v>
       </c>
       <c r="N79">
-        <v>12.7042306</v>
+        <v>12.6614284</v>
       </c>
       <c r="O79">
-        <v>3.41235633916</v>
+        <v>3.40085966824</v>
       </c>
       <c r="P79">
-        <v>9.29187426084</v>
+        <v>9.260568731759999</v>
       </c>
       <c r="Q79">
-        <v>10.79187426084</v>
+        <v>10.76056873176</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2059895368760334</v>
+        <v>0.2127037598712117</v>
       </c>
       <c r="T79">
-        <v>3.122392234342083</v>
+        <v>3.253264937694798</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.854708584890679</v>
+        <v>4.792468731238234</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07834303477166657</v>
+        <v>0.07816473266184548</v>
       </c>
       <c r="C80">
-        <v>18.87463485489356</v>
+        <v>18.12714983047206</v>
       </c>
       <c r="D80">
-        <v>37.84663485489357</v>
+        <v>37.87314983047204</v>
       </c>
       <c r="E80">
-        <v>54.77199999999999</v>
+        <v>55.54599999999999</v>
       </c>
       <c r="F80">
-        <v>60.37199999999999</v>
+        <v>61.14599999999999</v>
       </c>
       <c r="G80">
         <v>41.4</v>
@@ -7841,28 +7841,28 @@
         <v>16</v>
       </c>
       <c r="M80">
-        <v>3.3385716</v>
+        <v>3.3813738</v>
       </c>
       <c r="N80">
-        <v>12.6614284</v>
+        <v>12.6186262</v>
       </c>
       <c r="O80">
-        <v>3.40085966824</v>
+        <v>3.38936299732</v>
       </c>
       <c r="P80">
-        <v>9.260568731759999</v>
+        <v>9.229263202679999</v>
       </c>
       <c r="Q80">
-        <v>10.76056873176</v>
+        <v>10.72926320268</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2127037598712117</v>
+        <v>0.2200574326754547</v>
       </c>
       <c r="T80">
-        <v>3.253264937694798</v>
+        <v>3.396601708033487</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.792468731238234</v>
+        <v>4.73180457008332</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07816473266184548</v>
+        <v>0.07798643055202439</v>
       </c>
       <c r="C81">
-        <v>18.12714983047206</v>
+        <v>17.37970198435308</v>
       </c>
       <c r="D81">
-        <v>37.87314983047204</v>
+        <v>37.89970198435309</v>
       </c>
       <c r="E81">
-        <v>55.54599999999999</v>
+        <v>56.31999999999999</v>
       </c>
       <c r="F81">
-        <v>61.14599999999999</v>
+        <v>61.91999999999999</v>
       </c>
       <c r="G81">
         <v>41.4</v>
@@ -7923,28 +7923,28 @@
         <v>16</v>
       </c>
       <c r="M81">
-        <v>3.3813738</v>
+        <v>3.424176</v>
       </c>
       <c r="N81">
-        <v>12.6186262</v>
+        <v>12.575824</v>
       </c>
       <c r="O81">
-        <v>3.38936299732</v>
+        <v>3.3778663264</v>
       </c>
       <c r="P81">
-        <v>9.229263202679999</v>
+        <v>9.197957673600001</v>
       </c>
       <c r="Q81">
-        <v>10.72926320268</v>
+        <v>10.6979576736</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2200574326754547</v>
+        <v>0.228146472760122</v>
       </c>
       <c r="T81">
-        <v>3.396601708033487</v>
+        <v>3.554272155406044</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.73180457008332</v>
+        <v>4.672657012957279</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.07798643055202439</v>
+        <v>0.07780812844220331</v>
       </c>
       <c r="C82">
-        <v>17.37970198435308</v>
+        <v>16.63229139478658</v>
       </c>
       <c r="D82">
-        <v>37.89970198435309</v>
+        <v>37.92629139478657</v>
       </c>
       <c r="E82">
-        <v>56.31999999999999</v>
+        <v>57.09399999999999</v>
       </c>
       <c r="F82">
-        <v>61.91999999999999</v>
+        <v>62.694</v>
       </c>
       <c r="G82">
         <v>41.4</v>
@@ -8005,28 +8005,28 @@
         <v>16</v>
       </c>
       <c r="M82">
-        <v>3.424176</v>
+        <v>3.4669782</v>
       </c>
       <c r="N82">
-        <v>12.575824</v>
+        <v>12.5330218</v>
       </c>
       <c r="O82">
-        <v>3.3778663264</v>
+        <v>3.36636965548</v>
       </c>
       <c r="P82">
-        <v>9.197957673600001</v>
+        <v>9.16665214452</v>
       </c>
       <c r="Q82">
-        <v>10.6979576736</v>
+        <v>10.66665214452</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.228146472760122</v>
+        <v>0.2370869907484384</v>
       </c>
       <c r="T82">
-        <v>3.554272155406044</v>
+        <v>3.728539491975712</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>4.672657012957279</v>
+        <v>4.614969889340522</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07780812844220331</v>
+        <v>0.0776298263323822</v>
       </c>
       <c r="C83">
-        <v>16.63229139478658</v>
+        <v>15.88491814024217</v>
       </c>
       <c r="D83">
-        <v>37.92629139478657</v>
+        <v>37.95291814024216</v>
       </c>
       <c r="E83">
-        <v>57.09399999999999</v>
+        <v>57.86799999999999</v>
       </c>
       <c r="F83">
-        <v>62.694</v>
+        <v>63.468</v>
       </c>
       <c r="G83">
         <v>41.4</v>
@@ -8087,28 +8087,28 @@
         <v>16</v>
       </c>
       <c r="M83">
-        <v>3.4669782</v>
+        <v>3.5097804</v>
       </c>
       <c r="N83">
-        <v>12.5330218</v>
+        <v>12.4902196</v>
       </c>
       <c r="O83">
-        <v>3.36636965548</v>
+        <v>3.35487298456</v>
       </c>
       <c r="P83">
-        <v>9.16665214452</v>
+        <v>9.13534661544</v>
       </c>
       <c r="Q83">
-        <v>10.66665214452</v>
+        <v>10.63534661544</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2370869907484384</v>
+        <v>0.2470208996243456</v>
       </c>
       <c r="T83">
-        <v>3.728539491975712</v>
+        <v>3.92216986594201</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>4.614969889340522</v>
+        <v>4.558689768738807</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.0776298263323822</v>
+        <v>0.0774515242225611</v>
       </c>
       <c r="C84">
-        <v>15.88491814024217</v>
+        <v>15.13758229940997</v>
       </c>
       <c r="D84">
-        <v>37.95291814024216</v>
+        <v>37.97958229940998</v>
       </c>
       <c r="E84">
-        <v>57.86799999999999</v>
+        <v>58.642</v>
       </c>
       <c r="F84">
-        <v>63.468</v>
+        <v>64.242</v>
       </c>
       <c r="G84">
         <v>41.4</v>
@@ -8169,28 +8169,28 @@
         <v>16</v>
       </c>
       <c r="M84">
-        <v>3.5097804</v>
+        <v>3.5525826</v>
       </c>
       <c r="N84">
-        <v>12.4902196</v>
+        <v>12.4474174</v>
       </c>
       <c r="O84">
-        <v>3.35487298456</v>
+        <v>3.34337631364</v>
       </c>
       <c r="P84">
-        <v>9.13534661544</v>
+        <v>9.104041086359999</v>
       </c>
       <c r="Q84">
-        <v>10.63534661544</v>
+        <v>10.60404108636</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2470208996243456</v>
+        <v>0.2581235036621242</v>
       </c>
       <c r="T84">
-        <v>3.92216986594201</v>
+        <v>4.138580283904344</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>4.558689768738807</v>
+        <v>4.503765795621472</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.0774515242225611</v>
+        <v>0.07880916211274003</v>
       </c>
       <c r="C85">
-        <v>15.13758229940997</v>
+        <v>14.16149299867622</v>
       </c>
       <c r="D85">
-        <v>37.97958229940998</v>
+        <v>37.77749299867623</v>
       </c>
       <c r="E85">
-        <v>58.642</v>
+        <v>59.416</v>
       </c>
       <c r="F85">
-        <v>64.242</v>
+        <v>65.01600000000001</v>
       </c>
       <c r="G85">
         <v>41.4</v>
@@ -8251,45 +8251,45 @@
         <v>16</v>
       </c>
       <c r="M85">
-        <v>3.5525826</v>
+        <v>3.757924800000001</v>
       </c>
       <c r="N85">
-        <v>12.4474174</v>
+        <v>12.2420752</v>
       </c>
       <c r="O85">
-        <v>3.34337631364</v>
+        <v>3.28822139872</v>
       </c>
       <c r="P85">
-        <v>9.104041086359999</v>
+        <v>8.953853801279999</v>
       </c>
       <c r="Q85">
-        <v>10.60404108636</v>
+        <v>10.45385380128</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2581235036621242</v>
+        <v>0.2706139332046252</v>
       </c>
       <c r="T85">
-        <v>4.138580283904344</v>
+        <v>4.38204200411197</v>
       </c>
       <c r="U85">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V85">
         <v>0.2686</v>
       </c>
       <c r="W85">
-        <v>0.04044642</v>
+        <v>0.04227492000000001</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y85">
-        <v>4.503765795621472</v>
+        <v>4.257669019880334</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.07880916211274003</v>
+        <v>0.07864914500291892</v>
       </c>
       <c r="C86">
-        <v>14.16149299867624</v>
+        <v>13.41120024972059</v>
       </c>
       <c r="D86">
-        <v>37.77749299867623</v>
+        <v>37.80120024972059</v>
       </c>
       <c r="E86">
-        <v>59.41599999999999</v>
+        <v>60.18999999999999</v>
       </c>
       <c r="F86">
-        <v>65.01599999999999</v>
+        <v>65.78999999999999</v>
       </c>
       <c r="G86">
         <v>41.4</v>
@@ -8333,28 +8333,28 @@
         <v>16</v>
       </c>
       <c r="M86">
-        <v>3.7579248</v>
+        <v>3.802662</v>
       </c>
       <c r="N86">
-        <v>12.2420752</v>
+        <v>12.197338</v>
       </c>
       <c r="O86">
-        <v>3.28822139872</v>
+        <v>3.2762049868</v>
       </c>
       <c r="P86">
-        <v>8.953853801280001</v>
+        <v>8.9211330132</v>
       </c>
       <c r="Q86">
-        <v>10.45385380128</v>
+        <v>10.4211330132</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2706139332046251</v>
+        <v>0.2847697533527928</v>
       </c>
       <c r="T86">
-        <v>4.382042004111967</v>
+        <v>4.657965287013941</v>
       </c>
       <c r="U86">
         <v>0.0578</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>4.257669019880334</v>
+        <v>4.207578796117036</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.07864914500291892</v>
+        <v>0.07848912789309784</v>
       </c>
       <c r="C87">
-        <v>13.41120024972059</v>
+        <v>12.66093727440175</v>
       </c>
       <c r="D87">
-        <v>37.80120024972059</v>
+        <v>37.82493727440174</v>
       </c>
       <c r="E87">
-        <v>60.18999999999999</v>
+        <v>60.96399999999999</v>
       </c>
       <c r="F87">
-        <v>65.78999999999999</v>
+        <v>66.56399999999999</v>
       </c>
       <c r="G87">
         <v>41.4</v>
@@ -8415,28 +8415,28 @@
         <v>16</v>
       </c>
       <c r="M87">
-        <v>3.802662</v>
+        <v>3.8473992</v>
       </c>
       <c r="N87">
-        <v>12.197338</v>
+        <v>12.1526008</v>
       </c>
       <c r="O87">
-        <v>3.2762049868</v>
+        <v>3.26418857488</v>
       </c>
       <c r="P87">
-        <v>8.9211330132</v>
+        <v>8.88841222512</v>
       </c>
       <c r="Q87">
-        <v>10.4211330132</v>
+        <v>10.38841222512</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2847697533527928</v>
+        <v>0.3009478335221273</v>
       </c>
       <c r="T87">
-        <v>4.657965287013941</v>
+        <v>4.973306181759056</v>
       </c>
       <c r="U87">
         <v>0.0578</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>4.207578796117036</v>
+        <v>4.158653461278465</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.07848912789309784</v>
+        <v>0.07832911078327673</v>
       </c>
       <c r="C88">
-        <v>12.66093727440175</v>
+        <v>11.91070412884343</v>
       </c>
       <c r="D88">
-        <v>37.82493727440174</v>
+        <v>37.84870412884342</v>
       </c>
       <c r="E88">
-        <v>60.96399999999999</v>
+        <v>61.73799999999999</v>
       </c>
       <c r="F88">
-        <v>66.56399999999999</v>
+        <v>67.33799999999999</v>
       </c>
       <c r="G88">
         <v>41.4</v>
@@ -8497,28 +8497,28 @@
         <v>16</v>
       </c>
       <c r="M88">
-        <v>3.8473992</v>
+        <v>3.8921364</v>
       </c>
       <c r="N88">
-        <v>12.1526008</v>
+        <v>12.1078636</v>
       </c>
       <c r="O88">
-        <v>3.26418857488</v>
+        <v>3.25217216296</v>
       </c>
       <c r="P88">
-        <v>8.88841222512</v>
+        <v>8.855691437040001</v>
       </c>
       <c r="Q88">
-        <v>10.38841222512</v>
+        <v>10.35569143704</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3009478335221273</v>
+        <v>0.3196148491021287</v>
       </c>
       <c r="T88">
-        <v>4.973306181759056</v>
+        <v>5.33716106031111</v>
       </c>
       <c r="U88">
         <v>0.0578</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>4.158653461278465</v>
+        <v>4.110852846781012</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.07832911078327673</v>
+        <v>0.07816909367345565</v>
       </c>
       <c r="C89">
-        <v>11.91070412884343</v>
+        <v>11.16050086931054</v>
       </c>
       <c r="D89">
-        <v>37.84870412884342</v>
+        <v>37.87250086931053</v>
       </c>
       <c r="E89">
-        <v>61.73799999999999</v>
+        <v>62.51199999999999</v>
       </c>
       <c r="F89">
-        <v>67.33799999999999</v>
+        <v>68.11199999999999</v>
       </c>
       <c r="G89">
         <v>41.4</v>
@@ -8579,28 +8579,28 @@
         <v>16</v>
       </c>
       <c r="M89">
-        <v>3.8921364</v>
+        <v>3.9368736</v>
       </c>
       <c r="N89">
-        <v>12.1078636</v>
+        <v>12.0631264</v>
       </c>
       <c r="O89">
-        <v>3.25217216296</v>
+        <v>3.24015575104</v>
       </c>
       <c r="P89">
-        <v>8.855691437040001</v>
+        <v>8.82297064896</v>
       </c>
       <c r="Q89">
-        <v>10.35569143704</v>
+        <v>10.32297064896</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3196148491021287</v>
+        <v>0.3413930339454637</v>
       </c>
       <c r="T89">
-        <v>5.33716106031111</v>
+        <v>5.761658418621841</v>
       </c>
       <c r="U89">
         <v>0.0578</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>4.110852846781012</v>
+        <v>4.064138609885774</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.07816909367345565</v>
+        <v>0.07800907656363455</v>
       </c>
       <c r="C90">
-        <v>11.16050086931054</v>
+        <v>10.41032755220954</v>
       </c>
       <c r="D90">
-        <v>37.87250086931053</v>
+        <v>37.89632755220953</v>
       </c>
       <c r="E90">
-        <v>62.51199999999999</v>
+        <v>63.28599999999999</v>
       </c>
       <c r="F90">
-        <v>68.11199999999999</v>
+        <v>68.886</v>
       </c>
       <c r="G90">
         <v>41.4</v>
@@ -8661,28 +8661,28 @@
         <v>16</v>
       </c>
       <c r="M90">
-        <v>3.9368736</v>
+        <v>3.9816108</v>
       </c>
       <c r="N90">
-        <v>12.0631264</v>
+        <v>12.0183892</v>
       </c>
       <c r="O90">
-        <v>3.24015575104</v>
+        <v>3.22813933912</v>
       </c>
       <c r="P90">
-        <v>8.82297064896</v>
+        <v>8.790249860879999</v>
       </c>
       <c r="Q90">
-        <v>10.32297064896</v>
+        <v>10.29024986088</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3413930339454637</v>
+        <v>0.3671308887603141</v>
       </c>
       <c r="T90">
-        <v>5.761658418621841</v>
+        <v>6.26333711480725</v>
       </c>
       <c r="U90">
         <v>0.0578</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>4.064138609885774</v>
+        <v>4.018474131123012</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.07800907656363455</v>
+        <v>0.08015296945381345</v>
       </c>
       <c r="C91">
-        <v>10.41032755220954</v>
+        <v>9.319569210976866</v>
       </c>
       <c r="D91">
-        <v>37.89632755220953</v>
+        <v>37.57956921097686</v>
       </c>
       <c r="E91">
-        <v>63.28599999999999</v>
+        <v>64.06</v>
       </c>
       <c r="F91">
-        <v>68.886</v>
+        <v>69.66</v>
       </c>
       <c r="G91">
         <v>41.4</v>
@@ -8743,45 +8743,45 @@
         <v>16</v>
       </c>
       <c r="M91">
-        <v>3.9816108</v>
+        <v>4.270157999999999</v>
       </c>
       <c r="N91">
-        <v>12.0183892</v>
+        <v>11.729842</v>
       </c>
       <c r="O91">
-        <v>3.22813933912</v>
+        <v>3.150635561200001</v>
       </c>
       <c r="P91">
-        <v>8.790249860879999</v>
+        <v>8.5792064388</v>
       </c>
       <c r="Q91">
-        <v>10.29024986088</v>
+        <v>10.0792064388</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3671308887603141</v>
+        <v>0.3980163145381346</v>
       </c>
       <c r="T91">
-        <v>6.26333711480725</v>
+        <v>6.86535155022974</v>
       </c>
       <c r="U91">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V91">
         <v>0.2686</v>
       </c>
       <c r="W91">
-        <v>0.04227492000000001</v>
+        <v>0.04483482</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y91">
-        <v>4.018474131123012</v>
+        <v>3.74693395420029</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08015296945381345</v>
+        <v>0.08001855134399236</v>
       </c>
       <c r="C92">
-        <v>9.319569210976866</v>
+        <v>8.565273696058313</v>
       </c>
       <c r="D92">
-        <v>37.57956921097686</v>
+        <v>37.59927369605831</v>
       </c>
       <c r="E92">
-        <v>64.06</v>
+        <v>64.834</v>
       </c>
       <c r="F92">
-        <v>69.66</v>
+        <v>70.434</v>
       </c>
       <c r="G92">
         <v>41.4</v>
@@ -8825,28 +8825,28 @@
         <v>16</v>
       </c>
       <c r="M92">
-        <v>4.270157999999999</v>
+        <v>4.3176042</v>
       </c>
       <c r="N92">
-        <v>11.729842</v>
+        <v>11.6823958</v>
       </c>
       <c r="O92">
-        <v>3.150635561200001</v>
+        <v>3.13789151188</v>
       </c>
       <c r="P92">
-        <v>8.5792064388</v>
+        <v>8.544504288120001</v>
       </c>
       <c r="Q92">
-        <v>10.0792064388</v>
+        <v>10.04450428812</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3980163145381346</v>
+        <v>0.4357651682665818</v>
       </c>
       <c r="T92">
-        <v>6.86535155022974</v>
+        <v>7.601146971301674</v>
       </c>
       <c r="U92">
         <v>0.0613</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.74693395420029</v>
+        <v>3.705758855802484</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08001855134399236</v>
+        <v>0.07988413323417128</v>
       </c>
       <c r="C93">
-        <v>8.565273696058313</v>
+        <v>7.810998855694095</v>
       </c>
       <c r="D93">
-        <v>37.59927369605831</v>
+        <v>37.6189988556941</v>
       </c>
       <c r="E93">
-        <v>64.834</v>
+        <v>65.608</v>
       </c>
       <c r="F93">
-        <v>70.434</v>
+        <v>71.208</v>
       </c>
       <c r="G93">
         <v>41.4</v>
@@ -8907,28 +8907,28 @@
         <v>16</v>
       </c>
       <c r="M93">
-        <v>4.3176042</v>
+        <v>4.3650504</v>
       </c>
       <c r="N93">
-        <v>11.6823958</v>
+        <v>11.6349496</v>
       </c>
       <c r="O93">
-        <v>3.13789151188</v>
+        <v>3.12514746256</v>
       </c>
       <c r="P93">
-        <v>8.544504288120001</v>
+        <v>8.509802137439999</v>
       </c>
       <c r="Q93">
-        <v>10.04450428812</v>
+        <v>10.00980213744</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4357651682665818</v>
+        <v>0.4829512354271411</v>
       </c>
       <c r="T93">
-        <v>7.601146971301674</v>
+        <v>8.520891247641593</v>
       </c>
       <c r="U93">
         <v>0.0613</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.705758855802484</v>
+        <v>3.665478868239413</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.07988413323417128</v>
+        <v>0.07974971512435017</v>
       </c>
       <c r="C94">
-        <v>7.810998855694095</v>
+        <v>7.056744722439902</v>
       </c>
       <c r="D94">
-        <v>37.6189988556941</v>
+        <v>37.6387447224399</v>
       </c>
       <c r="E94">
-        <v>65.608</v>
+        <v>66.38200000000001</v>
       </c>
       <c r="F94">
-        <v>71.208</v>
+        <v>71.982</v>
       </c>
       <c r="G94">
         <v>41.4</v>
@@ -8989,28 +8989,28 @@
         <v>16</v>
       </c>
       <c r="M94">
-        <v>4.3650504</v>
+        <v>4.4124966</v>
       </c>
       <c r="N94">
-        <v>11.6349496</v>
+        <v>11.5875034</v>
       </c>
       <c r="O94">
-        <v>3.12514746256</v>
+        <v>3.11240341324</v>
       </c>
       <c r="P94">
-        <v>8.509802137439999</v>
+        <v>8.47509998676</v>
       </c>
       <c r="Q94">
-        <v>10.00980213744</v>
+        <v>9.97509998676</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4829512354271411</v>
+        <v>0.5436190360621456</v>
       </c>
       <c r="T94">
-        <v>8.520891247641593</v>
+        <v>9.703419602935771</v>
       </c>
       <c r="U94">
         <v>0.0613</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.665478868239413</v>
+        <v>3.626065116968022</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.07974971512435017</v>
+        <v>0.07961529701452907</v>
       </c>
       <c r="C95">
-        <v>7.056744722439902</v>
+        <v>6.302511328919735</v>
       </c>
       <c r="D95">
-        <v>37.6387447224399</v>
+        <v>37.65851132891973</v>
       </c>
       <c r="E95">
-        <v>66.38200000000001</v>
+        <v>67.15600000000001</v>
       </c>
       <c r="F95">
-        <v>71.982</v>
+        <v>72.756</v>
       </c>
       <c r="G95">
         <v>41.4</v>
@@ -9071,28 +9071,28 @@
         <v>16</v>
       </c>
       <c r="M95">
-        <v>4.4124966</v>
+        <v>4.4599428</v>
       </c>
       <c r="N95">
-        <v>11.5875034</v>
+        <v>11.5400572</v>
       </c>
       <c r="O95">
-        <v>3.11240341324</v>
+        <v>3.09965936392</v>
       </c>
       <c r="P95">
-        <v>8.47509998676</v>
+        <v>8.440397836079999</v>
       </c>
       <c r="Q95">
-        <v>9.97509998676</v>
+        <v>9.940397836079999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5436190360621456</v>
+        <v>0.6245094369088183</v>
       </c>
       <c r="T95">
-        <v>9.703419602935771</v>
+        <v>11.28012407666134</v>
       </c>
       <c r="U95">
         <v>0.0613</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.626065116968022</v>
+        <v>3.587489956149213</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.07961529701452907</v>
+        <v>0.07948087890470798</v>
       </c>
       <c r="C96">
-        <v>6.302511328919735</v>
+        <v>5.548298707826206</v>
       </c>
       <c r="D96">
-        <v>37.65851132891973</v>
+        <v>37.67829870782622</v>
       </c>
       <c r="E96">
-        <v>67.15600000000001</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="F96">
-        <v>72.756</v>
+        <v>73.53</v>
       </c>
       <c r="G96">
         <v>41.4</v>
@@ -9153,28 +9153,28 @@
         <v>16</v>
       </c>
       <c r="M96">
-        <v>4.4599428</v>
+        <v>4.507389</v>
       </c>
       <c r="N96">
-        <v>11.5400572</v>
+        <v>11.492611</v>
       </c>
       <c r="O96">
-        <v>3.09965936392</v>
+        <v>3.0869153146</v>
       </c>
       <c r="P96">
-        <v>8.440397836079999</v>
+        <v>8.4056956854</v>
       </c>
       <c r="Q96">
-        <v>9.940397836079999</v>
+        <v>9.9056956854</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6245094369088183</v>
+        <v>0.7377559980941605</v>
       </c>
       <c r="T96">
-        <v>11.28012407666134</v>
+        <v>13.48751033987715</v>
       </c>
       <c r="U96">
         <v>0.0613</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.587489956149213</v>
+        <v>3.549726903979222</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.07948087890470798</v>
+        <v>0.07934646079488689</v>
       </c>
       <c r="C97">
-        <v>5.548298707826206</v>
+        <v>4.794106891920691</v>
       </c>
       <c r="D97">
-        <v>37.67829870782622</v>
+        <v>37.69810689192069</v>
       </c>
       <c r="E97">
-        <v>67.93000000000001</v>
+        <v>68.70400000000001</v>
       </c>
       <c r="F97">
-        <v>73.53</v>
+        <v>74.304</v>
       </c>
       <c r="G97">
         <v>41.4</v>
@@ -9235,28 +9235,28 @@
         <v>16</v>
       </c>
       <c r="M97">
-        <v>4.507389</v>
+        <v>4.5548352</v>
       </c>
       <c r="N97">
-        <v>11.492611</v>
+        <v>11.4451648</v>
       </c>
       <c r="O97">
-        <v>3.0869153146</v>
+        <v>3.07417126528</v>
       </c>
       <c r="P97">
-        <v>8.4056956854</v>
+        <v>8.37099353472</v>
       </c>
       <c r="Q97">
-        <v>9.9056956854</v>
+        <v>9.87099353472</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7377559980941605</v>
+        <v>0.9076258398721736</v>
       </c>
       <c r="T97">
-        <v>13.48751033987715</v>
+        <v>16.79858973470086</v>
       </c>
       <c r="U97">
         <v>0.0613</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.549726903979222</v>
+        <v>3.512750582062771</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.07934646079488689</v>
+        <v>0.08119852508506581</v>
       </c>
       <c r="C98">
-        <v>4.794106891920705</v>
+        <v>3.749002409632723</v>
       </c>
       <c r="D98">
-        <v>37.69810689192069</v>
+        <v>37.42700240963271</v>
       </c>
       <c r="E98">
-        <v>68.70399999999999</v>
+        <v>69.47799999999999</v>
       </c>
       <c r="F98">
-        <v>74.30399999999999</v>
+        <v>75.07799999999999</v>
       </c>
       <c r="G98">
         <v>41.4</v>
@@ -9317,45 +9317,45 @@
         <v>16</v>
       </c>
       <c r="M98">
-        <v>4.554835199999999</v>
+        <v>4.812499799999999</v>
       </c>
       <c r="N98">
-        <v>11.4451648</v>
+        <v>11.1875002</v>
       </c>
       <c r="O98">
-        <v>3.07417126528</v>
+        <v>3.00496255372</v>
       </c>
       <c r="P98">
-        <v>8.37099353472</v>
+        <v>8.18253764628</v>
       </c>
       <c r="Q98">
-        <v>9.87099353472</v>
+        <v>9.68253764628</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9076258398721713</v>
+        <v>1.190742242835526</v>
       </c>
       <c r="T98">
-        <v>16.79858973470081</v>
+        <v>22.3170553927403</v>
       </c>
       <c r="U98">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V98">
         <v>0.2686</v>
       </c>
       <c r="W98">
-        <v>0.04483482</v>
+        <v>0.04688274000000001</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y98">
-        <v>3.512750582062772</v>
+        <v>3.324675462843656</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.08119852508506581</v>
+        <v>0.08108458617524469</v>
       </c>
       <c r="C99">
-        <v>3.749002409632723</v>
+        <v>2.99156813227043</v>
       </c>
       <c r="D99">
-        <v>37.42700240963271</v>
+        <v>37.44356813227042</v>
       </c>
       <c r="E99">
-        <v>69.47799999999999</v>
+        <v>70.252</v>
       </c>
       <c r="F99">
-        <v>75.07799999999999</v>
+        <v>75.85199999999999</v>
       </c>
       <c r="G99">
         <v>41.4</v>
@@ -9399,28 +9399,28 @@
         <v>16</v>
       </c>
       <c r="M99">
-        <v>4.812499799999999</v>
+        <v>4.8621132</v>
       </c>
       <c r="N99">
-        <v>11.1875002</v>
+        <v>11.1378868</v>
       </c>
       <c r="O99">
-        <v>3.00496255372</v>
+        <v>2.99163639448</v>
       </c>
       <c r="P99">
-        <v>8.18253764628</v>
+        <v>8.14625040552</v>
       </c>
       <c r="Q99">
-        <v>9.68253764628</v>
+        <v>9.64625040552</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.190742242835526</v>
+        <v>1.756975048762233</v>
       </c>
       <c r="T99">
-        <v>22.3170553927403</v>
+        <v>33.35398670881928</v>
       </c>
       <c r="U99">
         <v>0.0641</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.324675462843656</v>
+        <v>3.290750203018721</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.08108458617524469</v>
+        <v>0.08097064726542361</v>
       </c>
       <c r="C100">
-        <v>2.99156813227043</v>
+        <v>2.234148525849761</v>
       </c>
       <c r="D100">
-        <v>37.44356813227042</v>
+        <v>37.46014852584976</v>
       </c>
       <c r="E100">
-        <v>70.252</v>
+        <v>71.026</v>
       </c>
       <c r="F100">
-        <v>75.85199999999999</v>
+        <v>76.62599999999999</v>
       </c>
       <c r="G100">
         <v>41.4</v>
@@ -9481,28 +9481,28 @@
         <v>16</v>
       </c>
       <c r="M100">
-        <v>4.8621132</v>
+        <v>4.9117266</v>
       </c>
       <c r="N100">
-        <v>11.1378868</v>
+        <v>11.0882734</v>
       </c>
       <c r="O100">
-        <v>2.99163639448</v>
+        <v>2.97831023524</v>
       </c>
       <c r="P100">
-        <v>8.14625040552</v>
+        <v>8.10996316476</v>
       </c>
       <c r="Q100">
-        <v>9.64625040552</v>
+        <v>9.60996316476</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.756975048762233</v>
+        <v>3.455673466542357</v>
       </c>
       <c r="T100">
-        <v>33.35398670881928</v>
+        <v>66.46478065705621</v>
       </c>
       <c r="U100">
         <v>0.0641</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.290750203018721</v>
+        <v>3.257510301978127</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.08097064726542361</v>
-      </c>
-      <c r="C101">
-        <v>2.234148525849761</v>
-      </c>
-      <c r="D101">
-        <v>37.46014852584976</v>
-      </c>
-      <c r="E101">
-        <v>71.026</v>
-      </c>
-      <c r="F101">
-        <v>76.62599999999999</v>
-      </c>
-      <c r="G101">
-        <v>41.4</v>
-      </c>
-      <c r="H101">
-        <v>71.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>17.5</v>
-      </c>
-      <c r="K101">
-        <v>1.5</v>
-      </c>
-      <c r="L101">
-        <v>16</v>
-      </c>
-      <c r="M101">
-        <v>4.9117266</v>
-      </c>
-      <c r="N101">
-        <v>11.0882734</v>
-      </c>
-      <c r="O101">
-        <v>2.97831023524</v>
-      </c>
-      <c r="P101">
-        <v>8.10996316476</v>
-      </c>
-      <c r="Q101">
-        <v>9.60996316476</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.455673466542357</v>
-      </c>
-      <c r="T101">
-        <v>66.46478065705621</v>
-      </c>
-      <c r="U101">
-        <v>0.0641</v>
-      </c>
-      <c r="V101">
-        <v>0.2686</v>
-      </c>
-      <c r="W101">
-        <v>0.04688274000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba2/BB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.257510301978127</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
